--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121127551</v>
+        <v>121128629</v>
       </c>
       <c r="B7" t="n">
-        <v>90973</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,37 +1316,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625837</v>
+        <v>625981</v>
       </c>
       <c r="R7" t="n">
-        <v>6963681</v>
+        <v>6963750</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,9 +1383,19 @@
           <t>2024-11-11</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121128629</v>
+        <v>121127551</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
+        <v>90983</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,47 +1438,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625981</v>
+        <v>625837</v>
       </c>
       <c r="R8" t="n">
-        <v>6963750</v>
+        <v>6963681</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1485,19 +1495,9 @@
           <t>2024-11-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121128629</v>
+        <v>121127551</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>90983</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,47 +1316,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625981</v>
+        <v>625837</v>
       </c>
       <c r="R7" t="n">
-        <v>6963750</v>
+        <v>6963681</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1383,19 +1373,9 @@
           <t>2024-11-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121127551</v>
+        <v>121128629</v>
       </c>
       <c r="B8" t="n">
-        <v>90983</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,37 +1418,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625837</v>
+        <v>625981</v>
       </c>
       <c r="R8" t="n">
-        <v>6963681</v>
+        <v>6963750</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1495,9 +1485,19 @@
           <t>2024-11-11</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>121127551</v>
       </c>
       <c r="B7" t="n">
-        <v>90983</v>
+        <v>90995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121127551</v>
+        <v>121128629</v>
       </c>
       <c r="B7" t="n">
-        <v>90995</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,37 +1316,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625837</v>
+        <v>625981</v>
       </c>
       <c r="R7" t="n">
-        <v>6963681</v>
+        <v>6963750</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,9 +1383,19 @@
           <t>2024-11-11</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121128629</v>
+        <v>121127551</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>90996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,47 +1438,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625981</v>
+        <v>625837</v>
       </c>
       <c r="R8" t="n">
-        <v>6963750</v>
+        <v>6963681</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1485,19 +1495,9 @@
           <t>2024-11-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121128629</v>
+        <v>121127551</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>90999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,47 +1316,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625981</v>
+        <v>625837</v>
       </c>
       <c r="R7" t="n">
-        <v>6963750</v>
+        <v>6963681</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1383,19 +1373,9 @@
           <t>2024-11-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121127551</v>
+        <v>121128629</v>
       </c>
       <c r="B8" t="n">
-        <v>90996</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,37 +1418,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625837</v>
+        <v>625981</v>
       </c>
       <c r="R8" t="n">
-        <v>6963681</v>
+        <v>6963750</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1495,9 +1485,19 @@
           <t>2024-11-11</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1522,6 +1522,8093 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132998844</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57133</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>625974</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6963670</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132998866</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>625993</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6963697</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132998868</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>626006</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6963726</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132998853</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>625912</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6963674</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132998822</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91876</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>626041</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6963843</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132998859</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>658</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>625921</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6963711</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132998804</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>626083</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6963760</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132998821</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92373</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>626044</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6963850</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132998856</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101330</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>625873</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6963710</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132998852</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92333</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>625918</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6963673</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132998825</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>626036</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6963811</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132998857</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>625882</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6963712</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132998837</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>626063</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6963694</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132998863</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>658</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>625946</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6963712</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132998808</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>625958</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6963846</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132998820</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>626040</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6963847</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack på tall. Genomskinlig blänkande kåda syns med kikaren .</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132998819</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>626038</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6963844</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132998869</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>658</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>626014</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6963728</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132998876</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>658</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>626114</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6963731</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132998801</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91876</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>626119</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6963720</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132998872</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>626008</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6963810</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132998860</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>625929</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6963696</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132998851</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91863</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>112</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>625937</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6963688</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132998865</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>625994</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6963702</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132998849</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>658</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>625938</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6963688</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132998827</v>
+      </c>
+      <c r="B34" t="n">
+        <v>83177</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>626040</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6963809</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132998864</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>625948</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6963705</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132998802</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>658</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>626090</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6963723</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132998811</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>625999</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6963864</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Årsfärskt ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132998871</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>626014</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6963802</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132998836</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92333</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>626064</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6963694</v>
+      </c>
+      <c r="S39" t="n">
+        <v>6</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132998874</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>626066</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6963900</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132998814</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>658</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>626020</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6963869</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132998797</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92373</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>626154</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6963712</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132998830</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>658</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>626048</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6963766</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132998858</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>625898</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6963724</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132998875</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92373</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>626114</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6963731</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132998793</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>626130</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6963689</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132998824</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>626032</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6963816</v>
+      </c>
+      <c r="S47" t="n">
+        <v>6</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132998839</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>626063</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6963696</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132998833</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92373</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>626072</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6963711</v>
+      </c>
+      <c r="S49" t="n">
+        <v>6</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132998796</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>658</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>626152</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6963711</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132998854</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>625905</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6963675</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132998818</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>658</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>626014</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6963833</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132998794</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>626127</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6963690</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132998807</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>625962</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6963840</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132998841</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>626052</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6963684</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132998848</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>625948</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6963689</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132998843</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>626021</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6963665</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132998834</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>626079</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6963709</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132998813</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>626015</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6963874</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132998798</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>658</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>626159</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6963709</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132998829</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>626048</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6963765</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132998840</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>626055</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6963694</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132998805</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>626071</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6963769</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132998846</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>625949</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6963692</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132998842</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>658</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>626052</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6963682</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132998855</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101330</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>625891</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6963678</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132998870</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>626031</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6963761</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132998806</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>626016</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6963766</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132998845</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91876</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>625958</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6963695</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132998815</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>626009</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6963855</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132998832</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>626035</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6963715</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>132998795</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>626128</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6963704</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>132998809</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>625979</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6963852</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>132998817</v>
+      </c>
+      <c r="B74" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>658</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>626001</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6963850</v>
+      </c>
+      <c r="S74" t="n">
+        <v>6</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>132998823</v>
+      </c>
+      <c r="B75" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>658</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>626030</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6963820</v>
+      </c>
+      <c r="S75" t="n">
+        <v>6</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132998810</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>625992</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6963864</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>132998862</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92609</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>898</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>625946</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6963712</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>132998835</v>
+      </c>
+      <c r="B78" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>626076</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6963703</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>132998799</v>
+      </c>
+      <c r="B79" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>626135</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6963715</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>132998831</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>626039</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6963715</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>132998828</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lamsatjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>626045</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6963763</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1524,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132998844</v>
+        <v>132998868</v>
       </c>
       <c r="B9" t="n">
-        <v>57133</v>
+        <v>91913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,46 +1535,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625974</v>
+        <v>626006</v>
       </c>
       <c r="R9" t="n">
-        <v>6963670</v>
+        <v>6963726</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1606,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1616,7 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132998866</v>
+        <v>132998844</v>
       </c>
       <c r="B10" t="n">
-        <v>91913</v>
+        <v>57133</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,34 +1642,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625993</v>
+        <v>625974</v>
       </c>
       <c r="R10" t="n">
-        <v>6963697</v>
+        <v>6963670</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132998868</v>
+        <v>132998804</v>
       </c>
       <c r="B11" t="n">
-        <v>91913</v>
+        <v>79329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626006</v>
+        <v>626083</v>
       </c>
       <c r="R11" t="n">
-        <v>6963726</v>
+        <v>6963760</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1964,32 +1964,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132998822</v>
+        <v>132998859</v>
       </c>
       <c r="B13" t="n">
-        <v>91876</v>
+        <v>92212</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626041</v>
+        <v>625921</v>
       </c>
       <c r="R13" t="n">
-        <v>6963843</v>
+        <v>6963711</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2044,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132998859</v>
+        <v>132998866</v>
       </c>
       <c r="B14" t="n">
-        <v>92212</v>
+        <v>91913</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,21 +2087,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2106,10 +2111,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625921</v>
+        <v>625993</v>
       </c>
       <c r="R14" t="n">
-        <v>6963711</v>
+        <v>6963697</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2141,7 +2146,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,12 +2156,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,32 +2183,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132998804</v>
+        <v>132998822</v>
       </c>
       <c r="B15" t="n">
-        <v>79329</v>
+        <v>91876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2218,13 +2218,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626083</v>
+        <v>626041</v>
       </c>
       <c r="R15" t="n">
-        <v>6963760</v>
+        <v>6963843</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2397,32 +2397,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132998856</v>
+        <v>132998825</v>
       </c>
       <c r="B17" t="n">
-        <v>101330</v>
+        <v>79329</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625873</v>
+        <v>626036</v>
       </c>
       <c r="R17" t="n">
-        <v>6963710</v>
+        <v>6963811</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132998852</v>
+        <v>132998863</v>
       </c>
       <c r="B18" t="n">
-        <v>92333</v>
+        <v>92212</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040186</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>625918</v>
+        <v>625946</v>
       </c>
       <c r="R18" t="n">
-        <v>6963673</v>
+        <v>6963712</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,7 +2593,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2612,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132998825</v>
+        <v>132998837</v>
       </c>
       <c r="B19" t="n">
-        <v>79329</v>
+        <v>91913</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2623,21 +2622,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2647,13 +2646,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626036</v>
+        <v>626063</v>
       </c>
       <c r="R19" t="n">
-        <v>6963811</v>
+        <v>6963694</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2682,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2692,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,53 +2718,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132998857</v>
+        <v>132998856</v>
       </c>
       <c r="B20" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625882</v>
+        <v>625873</v>
       </c>
       <c r="R20" t="n">
-        <v>6963712</v>
+        <v>6963710</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2797,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,10 +2825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132998837</v>
+        <v>132998808</v>
       </c>
       <c r="B21" t="n">
-        <v>91913</v>
+        <v>79329</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,21 +2836,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2869,10 +2860,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626063</v>
+        <v>625958</v>
       </c>
       <c r="R21" t="n">
-        <v>6963694</v>
+        <v>6963846</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2904,7 +2895,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2914,7 +2905,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2941,10 +2932,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132998863</v>
+        <v>132998857</v>
       </c>
       <c r="B22" t="n">
-        <v>92212</v>
+        <v>57951</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,31 +2943,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625946</v>
+        <v>625882</v>
       </c>
       <c r="R22" t="n">
         <v>6963712</v>
@@ -3011,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3021,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132998808</v>
+        <v>132998852</v>
       </c>
       <c r="B23" t="n">
-        <v>79329</v>
+        <v>92333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,21 +3058,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3083,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625958</v>
+        <v>625918</v>
       </c>
       <c r="R23" t="n">
-        <v>6963846</v>
+        <v>6963673</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3118,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3128,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,6 +3136,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132998869</v>
+        <v>132998876</v>
       </c>
       <c r="B26" t="n">
         <v>92212</v>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626014</v>
+        <v>626114</v>
       </c>
       <c r="R26" t="n">
-        <v>6963728</v>
+        <v>6963731</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3502,7 +3502,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132998876</v>
+        <v>132998869</v>
       </c>
       <c r="B27" t="n">
         <v>92212</v>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626114</v>
+        <v>626014</v>
       </c>
       <c r="R27" t="n">
-        <v>6963731</v>
+        <v>6963728</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3836,10 +3836,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132998860</v>
+        <v>132998851</v>
       </c>
       <c r="B30" t="n">
-        <v>91927</v>
+        <v>91863</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3847,21 +3847,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625929</v>
+        <v>625937</v>
       </c>
       <c r="R30" t="n">
-        <v>6963696</v>
+        <v>6963688</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132998851</v>
+        <v>132998860</v>
       </c>
       <c r="B31" t="n">
-        <v>91863</v>
+        <v>91927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3954,21 +3954,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625937</v>
+        <v>625929</v>
       </c>
       <c r="R31" t="n">
-        <v>6963688</v>
+        <v>6963696</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4274,10 +4274,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132998827</v>
+        <v>132998864</v>
       </c>
       <c r="B34" t="n">
-        <v>83177</v>
+        <v>91913</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,21 +4285,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4309,13 +4309,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626040</v>
+        <v>625948</v>
       </c>
       <c r="R34" t="n">
-        <v>6963809</v>
+        <v>6963705</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4381,10 +4381,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132998864</v>
+        <v>132998827</v>
       </c>
       <c r="B35" t="n">
-        <v>91913</v>
+        <v>83177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,21 +4392,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625948</v>
+        <v>626040</v>
       </c>
       <c r="R35" t="n">
-        <v>6963705</v>
+        <v>6963809</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4595,10 +4595,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132998811</v>
+        <v>132998836</v>
       </c>
       <c r="B37" t="n">
-        <v>57954</v>
+        <v>92333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,45 +4606,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>625999</v>
+        <v>626064</v>
       </c>
       <c r="R37" t="n">
-        <v>6963864</v>
+        <v>6963694</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4673,7 +4665,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4683,12 +4675,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Årsfärskt ringhack på tall</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4697,6 +4684,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4715,10 +4703,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132998871</v>
+        <v>132998874</v>
       </c>
       <c r="B38" t="n">
-        <v>57954</v>
+        <v>79329</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4726,42 +4714,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626014</v>
+        <v>626066</v>
       </c>
       <c r="R38" t="n">
-        <v>6963802</v>
+        <v>6963900</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4793,7 +4773,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,12 +4783,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,10 +4810,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132998836</v>
+        <v>132998811</v>
       </c>
       <c r="B39" t="n">
-        <v>92333</v>
+        <v>57954</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4846,37 +4821,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626064</v>
+        <v>625999</v>
       </c>
       <c r="R39" t="n">
-        <v>6963694</v>
+        <v>6963864</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4905,7 +4888,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4915,7 +4898,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Årsfärskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4924,7 +4912,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4943,10 +4930,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132998874</v>
+        <v>132998871</v>
       </c>
       <c r="B40" t="n">
-        <v>79329</v>
+        <v>57954</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4954,34 +4941,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626066</v>
+        <v>626014</v>
       </c>
       <c r="R40" t="n">
-        <v>6963900</v>
+        <v>6963802</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5013,7 +5008,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5023,7 +5018,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5376,53 +5376,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132998858</v>
+        <v>132998875</v>
       </c>
       <c r="B44" t="n">
-        <v>57954</v>
+        <v>92373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>625898</v>
+        <v>626114</v>
       </c>
       <c r="R44" t="n">
-        <v>6963724</v>
+        <v>6963731</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5454,7 +5446,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5464,12 +5456,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5496,32 +5483,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132998875</v>
+        <v>132998824</v>
       </c>
       <c r="B45" t="n">
-        <v>92373</v>
+        <v>91927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5531,13 +5518,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626114</v>
+        <v>626032</v>
       </c>
       <c r="R45" t="n">
-        <v>6963731</v>
+        <v>6963816</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5566,7 +5553,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5576,7 +5563,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5603,32 +5590,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132998793</v>
+        <v>132998833</v>
       </c>
       <c r="B46" t="n">
-        <v>91913</v>
+        <v>92373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5638,13 +5625,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626130</v>
+        <v>626072</v>
       </c>
       <c r="R46" t="n">
-        <v>6963689</v>
+        <v>6963711</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5673,7 +5660,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5683,7 +5670,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5710,10 +5697,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132998824</v>
+        <v>132998839</v>
       </c>
       <c r="B47" t="n">
-        <v>91927</v>
+        <v>57954</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5721,37 +5708,45 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626032</v>
+        <v>626063</v>
       </c>
       <c r="R47" t="n">
-        <v>6963816</v>
+        <v>6963696</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5780,7 +5775,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5790,7 +5785,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5817,7 +5817,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132998839</v>
+        <v>132998858</v>
       </c>
       <c r="B48" t="n">
         <v>57954</v>
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626063</v>
+        <v>625898</v>
       </c>
       <c r="R48" t="n">
-        <v>6963696</v>
+        <v>6963724</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5937,32 +5937,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132998833</v>
+        <v>132998793</v>
       </c>
       <c r="B49" t="n">
-        <v>92373</v>
+        <v>91913</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>626072</v>
+        <v>626130</v>
       </c>
       <c r="R49" t="n">
-        <v>6963711</v>
+        <v>6963689</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6044,10 +6044,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132998796</v>
+        <v>132998794</v>
       </c>
       <c r="B50" t="n">
-        <v>92212</v>
+        <v>57951</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6055,34 +6055,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626152</v>
+        <v>626127</v>
       </c>
       <c r="R50" t="n">
-        <v>6963711</v>
+        <v>6963690</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6114,7 +6122,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6124,7 +6132,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6151,32 +6159,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132998854</v>
+        <v>132998818</v>
       </c>
       <c r="B51" t="n">
-        <v>97987</v>
+        <v>92212</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6186,10 +6194,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>625905</v>
+        <v>626014</v>
       </c>
       <c r="R51" t="n">
-        <v>6963675</v>
+        <v>6963833</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6221,7 +6229,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6231,7 +6239,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6258,7 +6266,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132998818</v>
+        <v>132998796</v>
       </c>
       <c r="B52" t="n">
         <v>92212</v>
@@ -6293,10 +6301,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626014</v>
+        <v>626152</v>
       </c>
       <c r="R52" t="n">
-        <v>6963833</v>
+        <v>6963711</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6328,7 +6336,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6338,7 +6346,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6365,53 +6373,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132998794</v>
+        <v>132998854</v>
       </c>
       <c r="B53" t="n">
-        <v>57951</v>
+        <v>97987</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626127</v>
+        <v>625905</v>
       </c>
       <c r="R53" t="n">
-        <v>6963690</v>
+        <v>6963675</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6480,10 +6480,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132998807</v>
+        <v>132998848</v>
       </c>
       <c r="B54" t="n">
-        <v>57954</v>
+        <v>91913</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6491,42 +6491,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>625962</v>
+        <v>625948</v>
       </c>
       <c r="R54" t="n">
-        <v>6963840</v>
+        <v>6963689</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6558,7 +6550,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6568,12 +6560,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6707,10 +6694,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132998848</v>
+        <v>132998807</v>
       </c>
       <c r="B56" t="n">
-        <v>91913</v>
+        <v>57954</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6718,34 +6705,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>625948</v>
+        <v>625962</v>
       </c>
       <c r="R56" t="n">
-        <v>6963689</v>
+        <v>6963840</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6777,7 +6772,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6787,7 +6782,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7482,10 +7482,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132998805</v>
+        <v>132998842</v>
       </c>
       <c r="B63" t="n">
-        <v>91927</v>
+        <v>92212</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7493,21 +7493,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>626071</v>
+        <v>626052</v>
       </c>
       <c r="R63" t="n">
-        <v>6963769</v>
+        <v>6963682</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7696,10 +7696,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132998842</v>
+        <v>132998805</v>
       </c>
       <c r="B65" t="n">
-        <v>92212</v>
+        <v>91927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7707,21 +7707,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>626052</v>
+        <v>626071</v>
       </c>
       <c r="R65" t="n">
-        <v>6963682</v>
+        <v>6963769</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7803,45 +7803,53 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132998855</v>
+        <v>132998870</v>
       </c>
       <c r="B66" t="n">
-        <v>101330</v>
+        <v>57954</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>625891</v>
+        <v>626031</v>
       </c>
       <c r="R66" t="n">
-        <v>6963678</v>
+        <v>6963761</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7873,7 +7881,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7883,7 +7891,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7910,53 +7923,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132998870</v>
+        <v>132998855</v>
       </c>
       <c r="B67" t="n">
-        <v>57954</v>
+        <v>101330</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>626031</v>
+        <v>625891</v>
       </c>
       <c r="R67" t="n">
-        <v>6963761</v>
+        <v>6963678</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7988,7 +7993,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7998,12 +8003,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8030,7 +8030,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132998806</v>
+        <v>132998815</v>
       </c>
       <c r="B68" t="n">
         <v>57954</v>
@@ -8058,20 +8058,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8081,10 +8073,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>626016</v>
+        <v>626009</v>
       </c>
       <c r="R68" t="n">
-        <v>6963766</v>
+        <v>6963855</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8116,7 +8108,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8126,7 +8118,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8153,45 +8150,61 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132998845</v>
+        <v>132998806</v>
       </c>
       <c r="B69" t="n">
-        <v>91876</v>
+        <v>57954</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>625958</v>
+        <v>626016</v>
       </c>
       <c r="R69" t="n">
-        <v>6963695</v>
+        <v>6963766</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8223,7 +8236,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8233,7 +8246,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8260,53 +8273,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132998815</v>
+        <v>132998845</v>
       </c>
       <c r="B70" t="n">
-        <v>57954</v>
+        <v>91876</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>626009</v>
+        <v>625958</v>
       </c>
       <c r="R70" t="n">
-        <v>6963855</v>
+        <v>6963695</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8338,7 +8343,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8348,12 +8353,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8487,10 +8487,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132998795</v>
+        <v>132998817</v>
       </c>
       <c r="B72" t="n">
-        <v>91913</v>
+        <v>92212</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8498,21 +8498,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8522,13 +8522,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>626128</v>
+        <v>626001</v>
       </c>
       <c r="R72" t="n">
-        <v>6963704</v>
+        <v>6963850</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8714,10 +8714,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132998817</v>
+        <v>132998795</v>
       </c>
       <c r="B74" t="n">
-        <v>92212</v>
+        <v>91913</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8725,21 +8725,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8749,13 +8749,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>626001</v>
+        <v>626128</v>
       </c>
       <c r="R74" t="n">
-        <v>6963850</v>
+        <v>6963704</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8821,10 +8821,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132998823</v>
+        <v>132998828</v>
       </c>
       <c r="B75" t="n">
-        <v>92212</v>
+        <v>91913</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8832,21 +8832,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8856,13 +8856,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>626030</v>
+        <v>626045</v>
       </c>
       <c r="R75" t="n">
-        <v>6963820</v>
+        <v>6963763</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8901,7 +8901,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8928,10 +8933,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132998810</v>
+        <v>132998823</v>
       </c>
       <c r="B76" t="n">
-        <v>57954</v>
+        <v>92212</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8939,45 +8944,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>625992</v>
+        <v>626030</v>
       </c>
       <c r="R76" t="n">
-        <v>6963864</v>
+        <v>6963820</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9006,7 +9003,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9016,12 +9013,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9048,32 +9040,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132998862</v>
+        <v>132998799</v>
       </c>
       <c r="B77" t="n">
-        <v>92609</v>
+        <v>91913</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9083,10 +9075,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>625946</v>
+        <v>626135</v>
       </c>
       <c r="R77" t="n">
-        <v>6963712</v>
+        <v>6963715</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9118,7 +9110,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9128,7 +9120,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9155,54 +9147,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132998835</v>
+        <v>132998862</v>
       </c>
       <c r="B78" t="n">
-        <v>5199</v>
+        <v>92609</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>105930</v>
+        <v>898</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>626076</v>
+        <v>625946</v>
       </c>
       <c r="R78" t="n">
-        <v>6963703</v>
+        <v>6963712</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9234,7 +9217,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9244,7 +9227,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9253,7 +9236,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9272,10 +9254,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132998799</v>
+        <v>132998831</v>
       </c>
       <c r="B79" t="n">
-        <v>91913</v>
+        <v>57954</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9283,31 +9265,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>626135</v>
+        <v>626039</v>
       </c>
       <c r="R79" t="n">
         <v>6963715</v>
@@ -9342,7 +9332,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9352,7 +9342,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9379,7 +9374,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132998831</v>
+        <v>132998810</v>
       </c>
       <c r="B80" t="n">
         <v>57954</v>
@@ -9412,7 +9407,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -9422,10 +9417,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>626039</v>
+        <v>625992</v>
       </c>
       <c r="R80" t="n">
-        <v>6963715</v>
+        <v>6963864</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9457,7 +9452,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9467,12 +9462,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9499,45 +9494,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132998828</v>
+        <v>132998835</v>
       </c>
       <c r="B81" t="n">
-        <v>91913</v>
+        <v>5199</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>626045</v>
+        <v>626076</v>
       </c>
       <c r="R81" t="n">
-        <v>6963763</v>
+        <v>6963703</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9569,7 +9573,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9579,12 +9583,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9593,6 +9592,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1524,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132998868</v>
+        <v>132998804</v>
       </c>
       <c r="B9" t="n">
-        <v>91913</v>
+        <v>79329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,21 +1535,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626006</v>
+        <v>626083</v>
       </c>
       <c r="R9" t="n">
-        <v>6963726</v>
+        <v>6963760</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132998844</v>
+        <v>132998868</v>
       </c>
       <c r="B10" t="n">
-        <v>57133</v>
+        <v>91913</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,46 +1642,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625974</v>
+        <v>626006</v>
       </c>
       <c r="R10" t="n">
-        <v>6963670</v>
+        <v>6963726</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1713,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1723,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,32 +1738,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132998804</v>
+        <v>132998822</v>
       </c>
       <c r="B11" t="n">
-        <v>79329</v>
+        <v>91876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,13 +1773,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626083</v>
+        <v>626041</v>
       </c>
       <c r="R11" t="n">
-        <v>6963760</v>
+        <v>6963843</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,32 +1845,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132998853</v>
+        <v>132998821</v>
       </c>
       <c r="B12" t="n">
-        <v>91913</v>
+        <v>92373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1892,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>625912</v>
+        <v>626044</v>
       </c>
       <c r="R12" t="n">
-        <v>6963674</v>
+        <v>6963850</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1927,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132998859</v>
+        <v>132998844</v>
       </c>
       <c r="B13" t="n">
-        <v>92212</v>
+        <v>57133</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,34 +1963,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625921</v>
+        <v>625974</v>
       </c>
       <c r="R13" t="n">
-        <v>6963711</v>
+        <v>6963670</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,12 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,7 +2071,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132998866</v>
+        <v>132998853</v>
       </c>
       <c r="B14" t="n">
         <v>91913</v>
@@ -2111,10 +2106,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625993</v>
+        <v>625912</v>
       </c>
       <c r="R14" t="n">
-        <v>6963697</v>
+        <v>6963674</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2146,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2156,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,32 +2178,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132998822</v>
+        <v>132998859</v>
       </c>
       <c r="B15" t="n">
-        <v>91876</v>
+        <v>92212</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2218,13 +2213,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626041</v>
+        <v>625921</v>
       </c>
       <c r="R15" t="n">
-        <v>6963843</v>
+        <v>6963711</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2253,7 +2248,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2263,7 +2258,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,32 +2290,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132998821</v>
+        <v>132998866</v>
       </c>
       <c r="B16" t="n">
-        <v>92373</v>
+        <v>91913</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626044</v>
+        <v>625993</v>
       </c>
       <c r="R16" t="n">
-        <v>6963850</v>
+        <v>6963697</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -5376,32 +5376,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132998875</v>
+        <v>132998793</v>
       </c>
       <c r="B44" t="n">
-        <v>92373</v>
+        <v>91913</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626114</v>
+        <v>626130</v>
       </c>
       <c r="R44" t="n">
-        <v>6963731</v>
+        <v>6963689</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5483,32 +5483,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132998824</v>
+        <v>132998875</v>
       </c>
       <c r="B45" t="n">
-        <v>91927</v>
+        <v>92373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5518,13 +5518,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626032</v>
+        <v>626114</v>
       </c>
       <c r="R45" t="n">
-        <v>6963816</v>
+        <v>6963731</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5590,32 +5590,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132998833</v>
+        <v>132998824</v>
       </c>
       <c r="B46" t="n">
-        <v>92373</v>
+        <v>91927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626072</v>
+        <v>626032</v>
       </c>
       <c r="R46" t="n">
-        <v>6963711</v>
+        <v>6963816</v>
       </c>
       <c r="S46" t="n">
         <v>6</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5697,56 +5697,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132998839</v>
+        <v>132998833</v>
       </c>
       <c r="B47" t="n">
-        <v>57954</v>
+        <v>92373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626063</v>
+        <v>626072</v>
       </c>
       <c r="R47" t="n">
-        <v>6963696</v>
+        <v>6963711</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5775,7 +5767,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5785,12 +5777,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5817,7 +5804,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132998858</v>
+        <v>132998839</v>
       </c>
       <c r="B48" t="n">
         <v>57954</v>
@@ -5860,10 +5847,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>625898</v>
+        <v>626063</v>
       </c>
       <c r="R48" t="n">
-        <v>6963724</v>
+        <v>6963696</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5895,7 +5882,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5905,12 +5892,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5937,10 +5924,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132998793</v>
+        <v>132998858</v>
       </c>
       <c r="B49" t="n">
-        <v>91913</v>
+        <v>57954</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5948,34 +5935,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>626130</v>
+        <v>625898</v>
       </c>
       <c r="R49" t="n">
-        <v>6963689</v>
+        <v>6963724</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6007,7 +6002,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6017,7 +6012,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6044,10 +6044,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132998794</v>
+        <v>132998818</v>
       </c>
       <c r="B50" t="n">
-        <v>57951</v>
+        <v>92212</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6055,42 +6055,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626127</v>
+        <v>626014</v>
       </c>
       <c r="R50" t="n">
-        <v>6963690</v>
+        <v>6963833</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6122,7 +6114,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6132,7 +6124,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6159,7 +6151,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132998818</v>
+        <v>132998796</v>
       </c>
       <c r="B51" t="n">
         <v>92212</v>
@@ -6194,10 +6186,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626014</v>
+        <v>626152</v>
       </c>
       <c r="R51" t="n">
-        <v>6963833</v>
+        <v>6963711</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6229,7 +6221,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6239,7 +6231,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6266,10 +6258,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132998796</v>
+        <v>132998794</v>
       </c>
       <c r="B52" t="n">
-        <v>92212</v>
+        <v>57951</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6277,34 +6269,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626152</v>
+        <v>626127</v>
       </c>
       <c r="R52" t="n">
-        <v>6963711</v>
+        <v>6963690</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6934,10 +6934,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132998834</v>
+        <v>132998813</v>
       </c>
       <c r="B58" t="n">
-        <v>91927</v>
+        <v>91913</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6945,21 +6945,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626079</v>
+        <v>626015</v>
       </c>
       <c r="R58" t="n">
-        <v>6963709</v>
+        <v>6963874</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7041,10 +7041,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132998813</v>
+        <v>132998834</v>
       </c>
       <c r="B59" t="n">
-        <v>91913</v>
+        <v>91927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7052,21 +7052,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7076,10 +7076,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>626015</v>
+        <v>626079</v>
       </c>
       <c r="R59" t="n">
-        <v>6963874</v>
+        <v>6963709</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7482,32 +7482,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132998842</v>
+        <v>132998855</v>
       </c>
       <c r="B63" t="n">
-        <v>92212</v>
+        <v>101330</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>626052</v>
+        <v>625891</v>
       </c>
       <c r="R63" t="n">
-        <v>6963682</v>
+        <v>6963678</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7589,10 +7589,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132998846</v>
+        <v>132998805</v>
       </c>
       <c r="B64" t="n">
-        <v>91913</v>
+        <v>91927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7600,21 +7600,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>625949</v>
+        <v>626071</v>
       </c>
       <c r="R64" t="n">
-        <v>6963692</v>
+        <v>6963769</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7696,10 +7696,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132998805</v>
+        <v>132998870</v>
       </c>
       <c r="B65" t="n">
-        <v>91927</v>
+        <v>57954</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7707,34 +7707,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>626071</v>
+        <v>626031</v>
       </c>
       <c r="R65" t="n">
-        <v>6963769</v>
+        <v>6963761</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7766,7 +7774,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7776,7 +7784,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7803,10 +7816,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132998870</v>
+        <v>132998842</v>
       </c>
       <c r="B66" t="n">
-        <v>57954</v>
+        <v>92212</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7814,42 +7827,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>626031</v>
+        <v>626052</v>
       </c>
       <c r="R66" t="n">
-        <v>6963761</v>
+        <v>6963682</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7881,7 +7886,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7891,12 +7896,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7923,32 +7923,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132998855</v>
+        <v>132998846</v>
       </c>
       <c r="B67" t="n">
-        <v>101330</v>
+        <v>91913</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7958,10 +7958,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>625891</v>
+        <v>625949</v>
       </c>
       <c r="R67" t="n">
-        <v>6963678</v>
+        <v>6963692</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -2397,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132998863</v>
+        <v>132998825</v>
       </c>
       <c r="B17" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625946</v>
+        <v>626036</v>
       </c>
       <c r="R17" t="n">
-        <v>6963712</v>
+        <v>6963811</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132998837</v>
+        <v>132998808</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626063</v>
+        <v>625958</v>
       </c>
       <c r="R18" t="n">
-        <v>6963694</v>
+        <v>6963846</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,32 +2611,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132998825</v>
+        <v>132998856</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>101338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626036</v>
+        <v>625873</v>
       </c>
       <c r="R19" t="n">
-        <v>6963811</v>
+        <v>6963710</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,10 +2718,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132998808</v>
+        <v>132998852</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>92338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625958</v>
+        <v>625918</v>
       </c>
       <c r="R20" t="n">
-        <v>6963846</v>
+        <v>6963673</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,6 +2807,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2825,32 +2826,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132998856</v>
+        <v>132998863</v>
       </c>
       <c r="B21" t="n">
-        <v>101338</v>
+        <v>92217</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,10 +2861,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625873</v>
+        <v>625946</v>
       </c>
       <c r="R21" t="n">
-        <v>6963710</v>
+        <v>6963712</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2895,7 +2896,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2905,7 +2906,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2932,10 +2933,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132998857</v>
+        <v>132998837</v>
       </c>
       <c r="B22" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2943,42 +2944,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625882</v>
+        <v>626063</v>
       </c>
       <c r="R22" t="n">
-        <v>6963712</v>
+        <v>6963694</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3010,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132998852</v>
+        <v>132998857</v>
       </c>
       <c r="B23" t="n">
-        <v>92338</v>
+        <v>57955</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,34 +3051,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625918</v>
+        <v>625882</v>
       </c>
       <c r="R23" t="n">
-        <v>6963673</v>
+        <v>6963712</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3117,7 +3118,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3128,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,7 +3137,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3609,53 +3609,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132998872</v>
+        <v>132998801</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626008</v>
+        <v>626119</v>
       </c>
       <c r="R28" t="n">
-        <v>6963810</v>
+        <v>6963720</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3687,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3697,12 +3689,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,45 +3716,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132998801</v>
+        <v>132998872</v>
       </c>
       <c r="B29" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626119</v>
+        <v>626008</v>
       </c>
       <c r="R29" t="n">
-        <v>6963720</v>
+        <v>6963810</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3799,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3804,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,10 +3836,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132998860</v>
+        <v>132998851</v>
       </c>
       <c r="B30" t="n">
-        <v>91932</v>
+        <v>91868</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3847,21 +3847,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625929</v>
+        <v>625937</v>
       </c>
       <c r="R30" t="n">
-        <v>6963696</v>
+        <v>6963688</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132998849</v>
+        <v>132998860</v>
       </c>
       <c r="B31" t="n">
-        <v>92217</v>
+        <v>91932</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3954,21 +3954,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625938</v>
+        <v>625929</v>
       </c>
       <c r="R31" t="n">
-        <v>6963688</v>
+        <v>6963696</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132998851</v>
+        <v>132998849</v>
       </c>
       <c r="B32" t="n">
-        <v>91868</v>
+        <v>92217</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,21 +4061,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625937</v>
+        <v>625938</v>
       </c>
       <c r="R32" t="n">
         <v>6963688</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4595,10 +4595,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132998836</v>
+        <v>132998874</v>
       </c>
       <c r="B37" t="n">
-        <v>92338</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,21 +4606,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4630,13 +4630,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626064</v>
+        <v>626066</v>
       </c>
       <c r="R37" t="n">
-        <v>6963694</v>
+        <v>6963900</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4684,7 +4684,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4943,10 +4942,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132998874</v>
+        <v>132998836</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>92338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4954,21 +4953,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4978,13 +4977,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626066</v>
+        <v>626064</v>
       </c>
       <c r="R40" t="n">
-        <v>6963900</v>
+        <v>6963694</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5013,7 +5012,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5023,7 +5022,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5032,6 +5031,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -6044,32 +6044,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132998854</v>
+        <v>132998818</v>
       </c>
       <c r="B50" t="n">
-        <v>97995</v>
+        <v>92217</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>625905</v>
+        <v>626014</v>
       </c>
       <c r="R50" t="n">
-        <v>6963675</v>
+        <v>6963833</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6151,7 +6151,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132998818</v>
+        <v>132998796</v>
       </c>
       <c r="B51" t="n">
         <v>92217</v>
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626014</v>
+        <v>626152</v>
       </c>
       <c r="R51" t="n">
-        <v>6963833</v>
+        <v>6963711</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6258,10 +6258,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132998796</v>
+        <v>132998794</v>
       </c>
       <c r="B52" t="n">
-        <v>92217</v>
+        <v>57955</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6269,34 +6269,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626152</v>
+        <v>626127</v>
       </c>
       <c r="R52" t="n">
-        <v>6963711</v>
+        <v>6963690</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6328,7 +6336,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6338,7 +6346,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6365,53 +6373,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132998794</v>
+        <v>132998854</v>
       </c>
       <c r="B53" t="n">
-        <v>57955</v>
+        <v>97995</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626127</v>
+        <v>625905</v>
       </c>
       <c r="R53" t="n">
-        <v>6963690</v>
+        <v>6963675</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6480,10 +6480,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132998848</v>
+        <v>132998807</v>
       </c>
       <c r="B54" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6491,34 +6491,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>625948</v>
+        <v>625962</v>
       </c>
       <c r="R54" t="n">
-        <v>6963689</v>
+        <v>6963840</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6550,7 +6558,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6560,7 +6568,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6587,10 +6600,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132998841</v>
+        <v>132998843</v>
       </c>
       <c r="B55" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6598,34 +6611,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626052</v>
+        <v>626021</v>
       </c>
       <c r="R55" t="n">
-        <v>6963684</v>
+        <v>6963665</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6657,7 +6678,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6667,7 +6688,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6694,10 +6720,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132998807</v>
+        <v>132998848</v>
       </c>
       <c r="B56" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6705,42 +6731,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>625962</v>
+        <v>625948</v>
       </c>
       <c r="R56" t="n">
-        <v>6963840</v>
+        <v>6963689</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6772,7 +6790,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6782,12 +6800,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6814,10 +6827,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132998843</v>
+        <v>132998841</v>
       </c>
       <c r="B57" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6825,42 +6838,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626021</v>
+        <v>626052</v>
       </c>
       <c r="R57" t="n">
-        <v>6963665</v>
+        <v>6963684</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6892,7 +6897,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6902,12 +6907,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7148,10 +7148,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132998840</v>
+        <v>132998798</v>
       </c>
       <c r="B60" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7159,42 +7159,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>626055</v>
+        <v>626159</v>
       </c>
       <c r="R60" t="n">
-        <v>6963694</v>
+        <v>6963709</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7226,7 +7218,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7236,12 +7228,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack på tall</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7268,10 +7255,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132998798</v>
+        <v>132998829</v>
       </c>
       <c r="B61" t="n">
-        <v>92217</v>
+        <v>91932</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7279,21 +7266,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7303,10 +7290,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>626159</v>
+        <v>626048</v>
       </c>
       <c r="R61" t="n">
-        <v>6963709</v>
+        <v>6963765</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7338,7 +7325,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7348,7 +7335,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7375,10 +7362,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132998829</v>
+        <v>132998840</v>
       </c>
       <c r="B62" t="n">
-        <v>91932</v>
+        <v>57958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7386,34 +7373,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>626048</v>
+        <v>626055</v>
       </c>
       <c r="R62" t="n">
-        <v>6963765</v>
+        <v>6963694</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7445,7 +7440,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7455,7 +7450,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8821,10 +8821,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132998828</v>
+        <v>132998831</v>
       </c>
       <c r="B75" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8832,34 +8832,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>626045</v>
+        <v>626039</v>
       </c>
       <c r="R75" t="n">
-        <v>6963763</v>
+        <v>6963715</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8891,7 +8899,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8901,12 +8909,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Död fruktkropp</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8933,10 +8941,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132998823</v>
+        <v>132998810</v>
       </c>
       <c r="B76" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8944,37 +8952,45 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>626030</v>
+        <v>625992</v>
       </c>
       <c r="R76" t="n">
-        <v>6963820</v>
+        <v>6963864</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9003,7 +9019,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9013,7 +9029,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9040,45 +9061,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132998799</v>
+        <v>132998835</v>
       </c>
       <c r="B77" t="n">
-        <v>91918</v>
+        <v>5199</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>626135</v>
+        <v>626076</v>
       </c>
       <c r="R77" t="n">
-        <v>6963715</v>
+        <v>6963703</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9110,7 +9140,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9120,7 +9150,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9129,6 +9159,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9147,32 +9178,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132998862</v>
+        <v>132998828</v>
       </c>
       <c r="B78" t="n">
-        <v>92614</v>
+        <v>91918</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9182,10 +9213,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>625946</v>
+        <v>626045</v>
       </c>
       <c r="R78" t="n">
-        <v>6963712</v>
+        <v>6963763</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9217,7 +9248,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9227,7 +9258,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9254,10 +9290,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132998831</v>
+        <v>132998823</v>
       </c>
       <c r="B79" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9265,45 +9301,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>626039</v>
+        <v>626030</v>
       </c>
       <c r="R79" t="n">
-        <v>6963715</v>
+        <v>6963820</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9332,7 +9360,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9342,12 +9370,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9374,10 +9397,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132998810</v>
+        <v>132998799</v>
       </c>
       <c r="B80" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9385,42 +9408,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>625992</v>
+        <v>626135</v>
       </c>
       <c r="R80" t="n">
-        <v>6963864</v>
+        <v>6963715</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9452,7 +9467,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9462,12 +9477,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9494,54 +9504,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132998835</v>
+        <v>132998862</v>
       </c>
       <c r="B81" t="n">
-        <v>5199</v>
+        <v>92614</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>105930</v>
+        <v>898</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>626076</v>
+        <v>625946</v>
       </c>
       <c r="R81" t="n">
-        <v>6963703</v>
+        <v>6963712</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9573,7 +9574,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9583,7 +9584,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9592,7 +9593,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1524,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132998853</v>
+        <v>132998804</v>
       </c>
       <c r="B9" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,21 +1535,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625912</v>
+        <v>626083</v>
       </c>
       <c r="R9" t="n">
-        <v>6963674</v>
+        <v>6963760</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,32 +1631,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132998821</v>
+        <v>132998853</v>
       </c>
       <c r="B10" t="n">
-        <v>92378</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626044</v>
+        <v>625912</v>
       </c>
       <c r="R10" t="n">
-        <v>6963850</v>
+        <v>6963674</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,32 +1738,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132998859</v>
+        <v>132998822</v>
       </c>
       <c r="B11" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>625921</v>
+        <v>626041</v>
       </c>
       <c r="R11" t="n">
-        <v>6963711</v>
+        <v>6963843</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,12 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,32 +1845,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132998866</v>
+        <v>132998821</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>92378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>625993</v>
+        <v>626044</v>
       </c>
       <c r="R12" t="n">
-        <v>6963697</v>
+        <v>6963850</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1920,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132998868</v>
+        <v>132998859</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,21 +1963,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626006</v>
+        <v>625921</v>
       </c>
       <c r="R13" t="n">
-        <v>6963726</v>
+        <v>6963711</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2027,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2032,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132998804</v>
+        <v>132998866</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626083</v>
+        <v>625993</v>
       </c>
       <c r="R14" t="n">
-        <v>6963760</v>
+        <v>6963697</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,32 +2171,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132998822</v>
+        <v>132998868</v>
       </c>
       <c r="B15" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626041</v>
+        <v>626006</v>
       </c>
       <c r="R15" t="n">
-        <v>6963843</v>
+        <v>6963726</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2504,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132998808</v>
+        <v>132998863</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>625958</v>
+        <v>625946</v>
       </c>
       <c r="R18" t="n">
-        <v>6963846</v>
+        <v>6963712</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,32 +2611,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132998856</v>
+        <v>132998837</v>
       </c>
       <c r="B19" t="n">
-        <v>101338</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625873</v>
+        <v>626063</v>
       </c>
       <c r="R19" t="n">
-        <v>6963710</v>
+        <v>6963694</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,10 +2718,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132998852</v>
+        <v>132998808</v>
       </c>
       <c r="B20" t="n">
-        <v>92338</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625918</v>
+        <v>625958</v>
       </c>
       <c r="R20" t="n">
-        <v>6963673</v>
+        <v>6963846</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,7 +2807,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2826,10 +2825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132998863</v>
+        <v>132998857</v>
       </c>
       <c r="B21" t="n">
-        <v>92217</v>
+        <v>57955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2837,31 +2836,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625946</v>
+        <v>625882</v>
       </c>
       <c r="R21" t="n">
         <v>6963712</v>
@@ -2896,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2906,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2933,32 +2940,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132998837</v>
+        <v>132998856</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2968,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626063</v>
+        <v>625873</v>
       </c>
       <c r="R22" t="n">
-        <v>6963694</v>
+        <v>6963710</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3003,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132998857</v>
+        <v>132998852</v>
       </c>
       <c r="B23" t="n">
-        <v>57955</v>
+        <v>92338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,42 +3058,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6040186</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625882</v>
+        <v>625918</v>
       </c>
       <c r="R23" t="n">
-        <v>6963712</v>
+        <v>6963673</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3118,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3128,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,6 +3136,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3836,10 +3836,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132998851</v>
+        <v>132998860</v>
       </c>
       <c r="B30" t="n">
-        <v>91868</v>
+        <v>91932</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3847,21 +3847,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625937</v>
+        <v>625929</v>
       </c>
       <c r="R30" t="n">
-        <v>6963688</v>
+        <v>6963696</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132998860</v>
+        <v>132998849</v>
       </c>
       <c r="B31" t="n">
-        <v>91932</v>
+        <v>92217</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3954,21 +3954,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625929</v>
+        <v>625938</v>
       </c>
       <c r="R31" t="n">
-        <v>6963696</v>
+        <v>6963688</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132998849</v>
+        <v>132998851</v>
       </c>
       <c r="B32" t="n">
-        <v>92217</v>
+        <v>91868</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,21 +4061,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625938</v>
+        <v>625937</v>
       </c>
       <c r="R32" t="n">
         <v>6963688</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4595,10 +4595,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132998874</v>
+        <v>132998811</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,34 +4606,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626066</v>
+        <v>625999</v>
       </c>
       <c r="R37" t="n">
-        <v>6963900</v>
+        <v>6963864</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4665,7 +4673,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4675,7 +4683,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Årsfärskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4702,7 +4715,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132998811</v>
+        <v>132998871</v>
       </c>
       <c r="B38" t="n">
         <v>57958</v>
@@ -4745,10 +4758,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>625999</v>
+        <v>626014</v>
       </c>
       <c r="R38" t="n">
-        <v>6963864</v>
+        <v>6963802</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4780,7 +4793,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4790,12 +4803,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Årsfärskt ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4822,10 +4835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132998871</v>
+        <v>132998836</v>
       </c>
       <c r="B39" t="n">
-        <v>57958</v>
+        <v>92338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4833,45 +4846,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626014</v>
+        <v>626064</v>
       </c>
       <c r="R39" t="n">
-        <v>6963802</v>
+        <v>6963694</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4900,7 +4905,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4910,12 +4915,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4924,6 +4924,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4942,10 +4943,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132998836</v>
+        <v>132998874</v>
       </c>
       <c r="B40" t="n">
-        <v>92338</v>
+        <v>79333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4953,21 +4954,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4977,13 +4978,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626064</v>
+        <v>626066</v>
       </c>
       <c r="R40" t="n">
-        <v>6963694</v>
+        <v>6963900</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5012,7 +5013,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5022,7 +5023,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5031,7 +5032,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -7589,10 +7589,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132998842</v>
+        <v>132998846</v>
       </c>
       <c r="B64" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7600,21 +7600,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>626052</v>
+        <v>625949</v>
       </c>
       <c r="R64" t="n">
-        <v>6963682</v>
+        <v>6963692</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7696,10 +7696,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132998846</v>
+        <v>132998842</v>
       </c>
       <c r="B65" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7707,21 +7707,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>625949</v>
+        <v>626052</v>
       </c>
       <c r="R65" t="n">
-        <v>6963692</v>
+        <v>6963682</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8030,53 +8030,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132998815</v>
+        <v>132998845</v>
       </c>
       <c r="B68" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>626009</v>
+        <v>625958</v>
       </c>
       <c r="R68" t="n">
-        <v>6963855</v>
+        <v>6963695</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8108,7 +8100,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8118,12 +8110,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8150,7 +8137,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132998806</v>
+        <v>132998815</v>
       </c>
       <c r="B69" t="n">
         <v>57958</v>
@@ -8178,20 +8165,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8201,10 +8180,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>626016</v>
+        <v>626009</v>
       </c>
       <c r="R69" t="n">
-        <v>6963766</v>
+        <v>6963855</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8236,7 +8215,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8246,7 +8225,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8273,45 +8257,61 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132998845</v>
+        <v>132998806</v>
       </c>
       <c r="B70" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>625958</v>
+        <v>626016</v>
       </c>
       <c r="R70" t="n">
-        <v>6963695</v>
+        <v>6963766</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8380,10 +8380,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132998832</v>
+        <v>132998809</v>
       </c>
       <c r="B71" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8391,34 +8391,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>626035</v>
+        <v>625979</v>
       </c>
       <c r="R71" t="n">
-        <v>6963715</v>
+        <v>6963852</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8450,7 +8458,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8460,7 +8468,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8487,10 +8500,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132998817</v>
+        <v>132998832</v>
       </c>
       <c r="B72" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8498,21 +8511,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8522,13 +8535,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>626001</v>
+        <v>626035</v>
       </c>
       <c r="R72" t="n">
-        <v>6963850</v>
+        <v>6963715</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8557,7 +8570,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8567,7 +8580,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8594,10 +8607,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132998795</v>
+        <v>132998817</v>
       </c>
       <c r="B73" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8605,21 +8618,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8629,13 +8642,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>626128</v>
+        <v>626001</v>
       </c>
       <c r="R73" t="n">
-        <v>6963704</v>
+        <v>6963850</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8664,7 +8677,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8674,7 +8687,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8701,10 +8714,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132998809</v>
+        <v>132998795</v>
       </c>
       <c r="B74" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8712,42 +8725,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>625979</v>
+        <v>626128</v>
       </c>
       <c r="R74" t="n">
-        <v>6963852</v>
+        <v>6963704</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8779,7 +8784,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8789,12 +8794,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8821,10 +8821,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132998831</v>
+        <v>132998828</v>
       </c>
       <c r="B75" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8832,42 +8832,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>626039</v>
+        <v>626045</v>
       </c>
       <c r="R75" t="n">
-        <v>6963715</v>
+        <v>6963763</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8899,7 +8891,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8909,12 +8901,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8941,10 +8933,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132998810</v>
+        <v>132998823</v>
       </c>
       <c r="B76" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8952,45 +8944,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>625992</v>
+        <v>626030</v>
       </c>
       <c r="R76" t="n">
-        <v>6963864</v>
+        <v>6963820</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9019,7 +9003,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9029,12 +9013,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9061,54 +9040,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132998835</v>
+        <v>132998799</v>
       </c>
       <c r="B77" t="n">
-        <v>5199</v>
+        <v>91918</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>626076</v>
+        <v>626135</v>
       </c>
       <c r="R77" t="n">
-        <v>6963703</v>
+        <v>6963715</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9140,7 +9110,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9150,7 +9120,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9159,7 +9129,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9178,32 +9147,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132998828</v>
+        <v>132998862</v>
       </c>
       <c r="B78" t="n">
-        <v>91918</v>
+        <v>92614</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9213,10 +9182,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>626045</v>
+        <v>625946</v>
       </c>
       <c r="R78" t="n">
-        <v>6963763</v>
+        <v>6963712</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9248,7 +9217,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9258,12 +9227,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9290,10 +9254,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132998823</v>
+        <v>132998831</v>
       </c>
       <c r="B79" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9301,37 +9265,45 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>626030</v>
+        <v>626039</v>
       </c>
       <c r="R79" t="n">
-        <v>6963820</v>
+        <v>6963715</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9360,7 +9332,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9370,7 +9342,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9397,10 +9374,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132998799</v>
+        <v>132998810</v>
       </c>
       <c r="B80" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9408,34 +9385,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>626135</v>
+        <v>625992</v>
       </c>
       <c r="R80" t="n">
-        <v>6963715</v>
+        <v>6963864</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9467,7 +9452,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9477,7 +9462,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9504,45 +9494,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132998862</v>
+        <v>132998835</v>
       </c>
       <c r="B81" t="n">
-        <v>92614</v>
+        <v>5199</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>898</v>
+        <v>105930</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>625946</v>
+        <v>626076</v>
       </c>
       <c r="R81" t="n">
-        <v>6963712</v>
+        <v>6963703</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9574,7 +9573,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9584,7 +9583,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9593,6 +9592,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1524,32 +1524,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132998804</v>
+        <v>132998822</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,13 +1559,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626083</v>
+        <v>626041</v>
       </c>
       <c r="R9" t="n">
-        <v>6963760</v>
+        <v>6963843</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132998853</v>
+        <v>132998804</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,21 +1642,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625912</v>
+        <v>626083</v>
       </c>
       <c r="R10" t="n">
-        <v>6963674</v>
+        <v>6963760</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,32 +1738,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132998822</v>
+        <v>132998853</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626041</v>
+        <v>625912</v>
       </c>
       <c r="R11" t="n">
-        <v>6963843</v>
+        <v>6963674</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2397,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132998825</v>
+        <v>132998863</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626036</v>
+        <v>625946</v>
       </c>
       <c r="R17" t="n">
-        <v>6963811</v>
+        <v>6963712</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132998863</v>
+        <v>132998837</v>
       </c>
       <c r="B18" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>625946</v>
+        <v>626063</v>
       </c>
       <c r="R18" t="n">
-        <v>6963712</v>
+        <v>6963694</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132998837</v>
+        <v>132998808</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2622,21 +2622,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626063</v>
+        <v>625958</v>
       </c>
       <c r="R19" t="n">
-        <v>6963694</v>
+        <v>6963846</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,7 +2718,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132998808</v>
+        <v>132998825</v>
       </c>
       <c r="B20" t="n">
         <v>79333</v>
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625958</v>
+        <v>626036</v>
       </c>
       <c r="R20" t="n">
-        <v>6963846</v>
+        <v>6963811</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,10 +2825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132998857</v>
+        <v>132998852</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>92338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,42 +2836,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6040186</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625882</v>
+        <v>625918</v>
       </c>
       <c r="R21" t="n">
-        <v>6963712</v>
+        <v>6963673</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2903,7 +2895,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2905,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,6 +2914,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3047,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132998852</v>
+        <v>132998857</v>
       </c>
       <c r="B23" t="n">
-        <v>92338</v>
+        <v>57955</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,34 +3051,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625918</v>
+        <v>625882</v>
       </c>
       <c r="R23" t="n">
-        <v>6963673</v>
+        <v>6963712</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3117,7 +3118,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3128,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,7 +3137,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132998811</v>
+        <v>132998874</v>
       </c>
       <c r="B37" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,42 +4606,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>625999</v>
+        <v>626066</v>
       </c>
       <c r="R37" t="n">
-        <v>6963864</v>
+        <v>6963900</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4673,7 +4665,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4683,12 +4675,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Årsfärskt ringhack på tall</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4715,7 +4702,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132998871</v>
+        <v>132998811</v>
       </c>
       <c r="B38" t="n">
         <v>57958</v>
@@ -4758,10 +4745,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626014</v>
+        <v>625999</v>
       </c>
       <c r="R38" t="n">
-        <v>6963802</v>
+        <v>6963864</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4793,7 +4780,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,12 +4790,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Årsfärskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,10 +4822,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132998836</v>
+        <v>132998871</v>
       </c>
       <c r="B39" t="n">
-        <v>92338</v>
+        <v>57958</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4846,37 +4833,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626064</v>
+        <v>626014</v>
       </c>
       <c r="R39" t="n">
-        <v>6963694</v>
+        <v>6963802</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4905,7 +4900,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4915,7 +4910,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4924,7 +4924,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4943,10 +4942,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132998874</v>
+        <v>132998836</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>92338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4954,21 +4953,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4978,13 +4977,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626066</v>
+        <v>626064</v>
       </c>
       <c r="R40" t="n">
-        <v>6963900</v>
+        <v>6963694</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5013,7 +5012,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5023,7 +5022,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5032,6 +5031,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -6258,53 +6258,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132998794</v>
+        <v>132998854</v>
       </c>
       <c r="B52" t="n">
-        <v>57955</v>
+        <v>97995</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626127</v>
+        <v>625905</v>
       </c>
       <c r="R52" t="n">
-        <v>6963690</v>
+        <v>6963675</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6336,7 +6328,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6346,7 +6338,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6373,45 +6365,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132998854</v>
+        <v>132998794</v>
       </c>
       <c r="B53" t="n">
-        <v>97995</v>
+        <v>57955</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>625905</v>
+        <v>626127</v>
       </c>
       <c r="R53" t="n">
-        <v>6963675</v>
+        <v>6963690</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6480,10 +6480,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132998807</v>
+        <v>132998848</v>
       </c>
       <c r="B54" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6491,42 +6491,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>625962</v>
+        <v>625948</v>
       </c>
       <c r="R54" t="n">
-        <v>6963840</v>
+        <v>6963689</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6558,7 +6550,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6568,12 +6560,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6600,10 +6587,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132998843</v>
+        <v>132998841</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6611,42 +6598,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626021</v>
+        <v>626052</v>
       </c>
       <c r="R55" t="n">
-        <v>6963665</v>
+        <v>6963684</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6678,7 +6657,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6688,12 +6667,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6720,10 +6694,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132998848</v>
+        <v>132998807</v>
       </c>
       <c r="B56" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6731,34 +6705,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>625948</v>
+        <v>625962</v>
       </c>
       <c r="R56" t="n">
-        <v>6963689</v>
+        <v>6963840</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6790,7 +6772,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6800,7 +6782,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6827,10 +6814,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132998841</v>
+        <v>132998843</v>
       </c>
       <c r="B57" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6838,34 +6825,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626052</v>
+        <v>626021</v>
       </c>
       <c r="R57" t="n">
-        <v>6963684</v>
+        <v>6963665</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6897,7 +6892,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6907,7 +6902,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7589,10 +7589,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132998846</v>
+        <v>132998842</v>
       </c>
       <c r="B64" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7600,21 +7600,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>625949</v>
+        <v>626052</v>
       </c>
       <c r="R64" t="n">
-        <v>6963692</v>
+        <v>6963682</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7696,10 +7696,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132998842</v>
+        <v>132998846</v>
       </c>
       <c r="B65" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7707,21 +7707,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>626052</v>
+        <v>625949</v>
       </c>
       <c r="R65" t="n">
-        <v>6963682</v>
+        <v>6963692</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8380,10 +8380,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132998809</v>
+        <v>132998832</v>
       </c>
       <c r="B71" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8391,42 +8391,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>625979</v>
+        <v>626035</v>
       </c>
       <c r="R71" t="n">
-        <v>6963852</v>
+        <v>6963715</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8458,7 +8450,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8468,12 +8460,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8500,10 +8487,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132998832</v>
+        <v>132998817</v>
       </c>
       <c r="B72" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8511,21 +8498,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8535,13 +8522,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>626035</v>
+        <v>626001</v>
       </c>
       <c r="R72" t="n">
-        <v>6963715</v>
+        <v>6963850</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8570,7 +8557,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8580,7 +8567,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8607,10 +8594,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132998817</v>
+        <v>132998795</v>
       </c>
       <c r="B73" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8618,21 +8605,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8642,13 +8629,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>626001</v>
+        <v>626128</v>
       </c>
       <c r="R73" t="n">
-        <v>6963850</v>
+        <v>6963704</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8677,7 +8664,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8687,7 +8674,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8714,10 +8701,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132998795</v>
+        <v>132998809</v>
       </c>
       <c r="B74" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8725,34 +8712,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>626128</v>
+        <v>625979</v>
       </c>
       <c r="R74" t="n">
-        <v>6963704</v>
+        <v>6963852</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8784,7 +8779,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8794,7 +8789,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8821,10 +8821,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132998828</v>
+        <v>132998831</v>
       </c>
       <c r="B75" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8832,34 +8832,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>626045</v>
+        <v>626039</v>
       </c>
       <c r="R75" t="n">
-        <v>6963763</v>
+        <v>6963715</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8891,7 +8899,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8901,12 +8909,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Död fruktkropp</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8933,10 +8941,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132998823</v>
+        <v>132998810</v>
       </c>
       <c r="B76" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8944,37 +8952,45 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>626030</v>
+        <v>625992</v>
       </c>
       <c r="R76" t="n">
-        <v>6963820</v>
+        <v>6963864</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9003,7 +9019,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9013,7 +9029,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9040,7 +9061,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132998799</v>
+        <v>132998828</v>
       </c>
       <c r="B77" t="n">
         <v>91918</v>
@@ -9075,10 +9096,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>626135</v>
+        <v>626045</v>
       </c>
       <c r="R77" t="n">
-        <v>6963715</v>
+        <v>6963763</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9110,7 +9131,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9120,7 +9141,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9147,32 +9173,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132998862</v>
+        <v>132998823</v>
       </c>
       <c r="B78" t="n">
-        <v>92614</v>
+        <v>92217</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9182,13 +9208,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>625946</v>
+        <v>626030</v>
       </c>
       <c r="R78" t="n">
-        <v>6963712</v>
+        <v>6963820</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9217,7 +9243,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9227,7 +9253,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9254,10 +9280,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132998831</v>
+        <v>132998799</v>
       </c>
       <c r="B79" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9265,39 +9291,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>626039</v>
+        <v>626135</v>
       </c>
       <c r="R79" t="n">
         <v>6963715</v>
@@ -9332,7 +9350,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9342,12 +9360,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9374,53 +9387,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132998810</v>
+        <v>132998862</v>
       </c>
       <c r="B80" t="n">
-        <v>57958</v>
+        <v>92614</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>625992</v>
+        <v>625946</v>
       </c>
       <c r="R80" t="n">
-        <v>6963864</v>
+        <v>6963712</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9452,7 +9457,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9462,12 +9467,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1524,32 +1524,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132998822</v>
+        <v>132998853</v>
       </c>
       <c r="B9" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,13 +1559,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626041</v>
+        <v>625912</v>
       </c>
       <c r="R9" t="n">
-        <v>6963843</v>
+        <v>6963674</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,32 +1631,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132998804</v>
+        <v>132998821</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>92378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626083</v>
+        <v>626044</v>
       </c>
       <c r="R10" t="n">
-        <v>6963760</v>
+        <v>6963850</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132998853</v>
+        <v>132998859</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>625912</v>
+        <v>625921</v>
       </c>
       <c r="R11" t="n">
-        <v>6963674</v>
+        <v>6963711</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1818,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,32 +1850,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132998821</v>
+        <v>132998866</v>
       </c>
       <c r="B12" t="n">
-        <v>92378</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626044</v>
+        <v>625993</v>
       </c>
       <c r="R12" t="n">
-        <v>6963850</v>
+        <v>6963697</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1915,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132998859</v>
+        <v>132998868</v>
       </c>
       <c r="B13" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,21 +1968,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1987,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625921</v>
+        <v>626006</v>
       </c>
       <c r="R13" t="n">
-        <v>6963711</v>
+        <v>6963726</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2022,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,12 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132998866</v>
+        <v>132998804</v>
       </c>
       <c r="B14" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625993</v>
+        <v>626083</v>
       </c>
       <c r="R14" t="n">
-        <v>6963697</v>
+        <v>6963760</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,32 +2171,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132998868</v>
+        <v>132998822</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626006</v>
+        <v>626041</v>
       </c>
       <c r="R15" t="n">
-        <v>6963726</v>
+        <v>6963843</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2611,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132998808</v>
+        <v>132998857</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2622,34 +2622,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625958</v>
+        <v>625882</v>
       </c>
       <c r="R19" t="n">
-        <v>6963846</v>
+        <v>6963712</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2681,7 +2689,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2699,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2825,10 +2833,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132998852</v>
+        <v>132998808</v>
       </c>
       <c r="B21" t="n">
-        <v>92338</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,21 +2844,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625918</v>
+        <v>625958</v>
       </c>
       <c r="R21" t="n">
-        <v>6963673</v>
+        <v>6963846</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2895,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2905,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2914,7 +2922,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2933,32 +2940,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132998856</v>
+        <v>132998852</v>
       </c>
       <c r="B22" t="n">
-        <v>101338</v>
+        <v>92338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>6040186</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2968,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625873</v>
+        <v>625918</v>
       </c>
       <c r="R22" t="n">
-        <v>6963710</v>
+        <v>6963673</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3003,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3022,6 +3029,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3040,53 +3048,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132998857</v>
+        <v>132998856</v>
       </c>
       <c r="B23" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625882</v>
+        <v>625873</v>
       </c>
       <c r="R23" t="n">
-        <v>6963712</v>
+        <v>6963710</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4595,10 +4595,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132998874</v>
+        <v>132998811</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,34 +4606,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626066</v>
+        <v>625999</v>
       </c>
       <c r="R37" t="n">
-        <v>6963900</v>
+        <v>6963864</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4665,7 +4673,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4675,7 +4683,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Årsfärskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4702,7 +4715,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132998811</v>
+        <v>132998871</v>
       </c>
       <c r="B38" t="n">
         <v>57958</v>
@@ -4745,10 +4758,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>625999</v>
+        <v>626014</v>
       </c>
       <c r="R38" t="n">
-        <v>6963864</v>
+        <v>6963802</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4780,7 +4793,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4790,12 +4803,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Årsfärskt ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4822,10 +4835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132998871</v>
+        <v>132998874</v>
       </c>
       <c r="B39" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4833,42 +4846,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626014</v>
+        <v>626066</v>
       </c>
       <c r="R39" t="n">
-        <v>6963802</v>
+        <v>6963900</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4900,7 +4905,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4910,12 +4915,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6258,45 +6258,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132998854</v>
+        <v>132998794</v>
       </c>
       <c r="B52" t="n">
-        <v>97995</v>
+        <v>57955</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>625905</v>
+        <v>626127</v>
       </c>
       <c r="R52" t="n">
-        <v>6963675</v>
+        <v>6963690</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6328,7 +6336,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6338,7 +6346,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6365,53 +6373,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132998794</v>
+        <v>132998854</v>
       </c>
       <c r="B53" t="n">
-        <v>57955</v>
+        <v>97995</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626127</v>
+        <v>625905</v>
       </c>
       <c r="R53" t="n">
-        <v>6963690</v>
+        <v>6963675</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -9061,45 +9061,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132998828</v>
+        <v>132998835</v>
       </c>
       <c r="B77" t="n">
-        <v>91918</v>
+        <v>5199</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>626045</v>
+        <v>626076</v>
       </c>
       <c r="R77" t="n">
-        <v>6963763</v>
+        <v>6963703</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9131,7 +9140,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9141,12 +9150,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9155,6 +9159,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9173,10 +9178,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132998823</v>
+        <v>132998828</v>
       </c>
       <c r="B78" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9184,21 +9189,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9208,13 +9213,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>626030</v>
+        <v>626045</v>
       </c>
       <c r="R78" t="n">
-        <v>6963820</v>
+        <v>6963763</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9243,7 +9248,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9253,7 +9258,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9280,10 +9290,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132998799</v>
+        <v>132998823</v>
       </c>
       <c r="B79" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9291,21 +9301,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9315,13 +9325,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>626135</v>
+        <v>626030</v>
       </c>
       <c r="R79" t="n">
-        <v>6963715</v>
+        <v>6963820</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9350,7 +9360,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9360,7 +9370,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9387,32 +9397,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132998862</v>
+        <v>132998799</v>
       </c>
       <c r="B80" t="n">
-        <v>92614</v>
+        <v>91918</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9422,10 +9432,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>625946</v>
+        <v>626135</v>
       </c>
       <c r="R80" t="n">
-        <v>6963712</v>
+        <v>6963715</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9457,7 +9467,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9467,7 +9477,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9494,54 +9504,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132998835</v>
+        <v>132998862</v>
       </c>
       <c r="B81" t="n">
-        <v>5199</v>
+        <v>92614</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>105930</v>
+        <v>898</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>626076</v>
+        <v>625946</v>
       </c>
       <c r="R81" t="n">
-        <v>6963703</v>
+        <v>6963712</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9573,7 +9574,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9583,7 +9584,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9592,7 +9593,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -2397,32 +2397,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132998863</v>
+        <v>132998856</v>
       </c>
       <c r="B17" t="n">
-        <v>92217</v>
+        <v>101338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625946</v>
+        <v>625873</v>
       </c>
       <c r="R17" t="n">
-        <v>6963712</v>
+        <v>6963710</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132998837</v>
+        <v>132998863</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626063</v>
+        <v>625946</v>
       </c>
       <c r="R18" t="n">
-        <v>6963694</v>
+        <v>6963712</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132998857</v>
+        <v>132998837</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2622,42 +2622,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625882</v>
+        <v>626063</v>
       </c>
       <c r="R19" t="n">
-        <v>6963712</v>
+        <v>6963694</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2689,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2699,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,10 +2718,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132998825</v>
+        <v>132998857</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2737,37 +2729,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626036</v>
+        <v>625882</v>
       </c>
       <c r="R20" t="n">
-        <v>6963811</v>
+        <v>6963712</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,7 +2833,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132998808</v>
+        <v>132998825</v>
       </c>
       <c r="B21" t="n">
         <v>79333</v>
@@ -2868,13 +2868,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625958</v>
+        <v>626036</v>
       </c>
       <c r="R21" t="n">
-        <v>6963846</v>
+        <v>6963811</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132998852</v>
+        <v>132998808</v>
       </c>
       <c r="B22" t="n">
-        <v>92338</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,21 +2951,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625918</v>
+        <v>625958</v>
       </c>
       <c r="R22" t="n">
-        <v>6963673</v>
+        <v>6963846</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3029,7 +3029,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3048,32 +3047,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132998856</v>
+        <v>132998852</v>
       </c>
       <c r="B23" t="n">
-        <v>101338</v>
+        <v>92338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>6040186</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3083,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625873</v>
+        <v>625918</v>
       </c>
       <c r="R23" t="n">
-        <v>6963710</v>
+        <v>6963673</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3118,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3128,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,6 +3136,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1524,7 +1524,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132998853</v>
+        <v>132998868</v>
       </c>
       <c r="B9" t="n">
         <v>91918</v>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625912</v>
+        <v>626006</v>
       </c>
       <c r="R9" t="n">
-        <v>6963674</v>
+        <v>6963726</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,32 +1631,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132998821</v>
+        <v>132998853</v>
       </c>
       <c r="B10" t="n">
-        <v>92378</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626044</v>
+        <v>625912</v>
       </c>
       <c r="R10" t="n">
-        <v>6963850</v>
+        <v>6963674</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132998859</v>
+        <v>132998866</v>
       </c>
       <c r="B11" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>625921</v>
+        <v>625993</v>
       </c>
       <c r="R11" t="n">
-        <v>6963711</v>
+        <v>6963697</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,12 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132998866</v>
+        <v>132998859</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,21 +1856,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>625993</v>
+        <v>625921</v>
       </c>
       <c r="R12" t="n">
-        <v>6963697</v>
+        <v>6963711</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1920,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1925,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,32 +1957,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132998868</v>
+        <v>132998821</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>92378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626006</v>
+        <v>626044</v>
       </c>
       <c r="R13" t="n">
-        <v>6963726</v>
+        <v>6963850</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2397,32 +2397,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132998856</v>
+        <v>132998837</v>
       </c>
       <c r="B17" t="n">
-        <v>101338</v>
+        <v>91918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625873</v>
+        <v>626063</v>
       </c>
       <c r="R17" t="n">
-        <v>6963710</v>
+        <v>6963694</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2611,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132998837</v>
+        <v>132998825</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2622,21 +2622,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626063</v>
+        <v>626036</v>
       </c>
       <c r="R19" t="n">
-        <v>6963694</v>
+        <v>6963811</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,10 +2718,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132998857</v>
+        <v>132998808</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,42 +2729,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625882</v>
+        <v>625958</v>
       </c>
       <c r="R20" t="n">
-        <v>6963712</v>
+        <v>6963846</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2796,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2806,7 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,10 +2825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132998825</v>
+        <v>132998857</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,37 +2836,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626036</v>
+        <v>625882</v>
       </c>
       <c r="R21" t="n">
-        <v>6963811</v>
+        <v>6963712</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132998808</v>
+        <v>132998852</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>92338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,21 +2951,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625958</v>
+        <v>625918</v>
       </c>
       <c r="R22" t="n">
-        <v>6963846</v>
+        <v>6963673</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3029,6 +3029,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3047,32 +3048,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132998852</v>
+        <v>132998856</v>
       </c>
       <c r="B23" t="n">
-        <v>92338</v>
+        <v>101338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3082,10 +3083,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625918</v>
+        <v>625873</v>
       </c>
       <c r="R23" t="n">
-        <v>6963673</v>
+        <v>6963710</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3117,7 +3118,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3128,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,7 +3137,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132998876</v>
+        <v>132998869</v>
       </c>
       <c r="B26" t="n">
         <v>92217</v>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626114</v>
+        <v>626014</v>
       </c>
       <c r="R26" t="n">
-        <v>6963731</v>
+        <v>6963728</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3502,7 +3502,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132998869</v>
+        <v>132998876</v>
       </c>
       <c r="B27" t="n">
         <v>92217</v>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626014</v>
+        <v>626114</v>
       </c>
       <c r="R27" t="n">
-        <v>6963728</v>
+        <v>6963731</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3836,45 +3836,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132998860</v>
+        <v>132998865</v>
       </c>
       <c r="B30" t="n">
-        <v>91932</v>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625929</v>
+        <v>625994</v>
       </c>
       <c r="R30" t="n">
-        <v>6963696</v>
+        <v>6963702</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3915,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3925,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3925,6 +3934,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4157,54 +4167,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132998865</v>
+        <v>132998860</v>
       </c>
       <c r="B33" t="n">
-        <v>5179</v>
+        <v>91932</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625994</v>
+        <v>625929</v>
       </c>
       <c r="R33" t="n">
-        <v>6963702</v>
+        <v>6963696</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4236,7 +4237,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4246,7 +4247,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4255,7 +4256,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4274,10 +4274,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132998864</v>
+        <v>132998827</v>
       </c>
       <c r="B34" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,21 +4285,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4309,13 +4309,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>625948</v>
+        <v>626040</v>
       </c>
       <c r="R34" t="n">
-        <v>6963705</v>
+        <v>6963809</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4381,10 +4381,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132998827</v>
+        <v>132998864</v>
       </c>
       <c r="B35" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,21 +4392,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626040</v>
+        <v>625948</v>
       </c>
       <c r="R35" t="n">
-        <v>6963809</v>
+        <v>6963705</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4595,10 +4595,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132998811</v>
+        <v>132998874</v>
       </c>
       <c r="B37" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,42 +4606,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>625999</v>
+        <v>626066</v>
       </c>
       <c r="R37" t="n">
-        <v>6963864</v>
+        <v>6963900</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4673,7 +4665,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4683,12 +4675,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Årsfärskt ringhack på tall</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4715,7 +4702,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132998871</v>
+        <v>132998811</v>
       </c>
       <c r="B38" t="n">
         <v>57958</v>
@@ -4758,10 +4745,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626014</v>
+        <v>625999</v>
       </c>
       <c r="R38" t="n">
-        <v>6963802</v>
+        <v>6963864</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4793,7 +4780,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,12 +4790,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Årsfärskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,10 +4822,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132998874</v>
+        <v>132998871</v>
       </c>
       <c r="B39" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4846,34 +4833,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626066</v>
+        <v>626014</v>
       </c>
       <c r="R39" t="n">
-        <v>6963900</v>
+        <v>6963802</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4905,7 +4900,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4915,7 +4910,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5483,10 +5483,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132998824</v>
+        <v>132998793</v>
       </c>
       <c r="B45" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5494,21 +5494,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5518,13 +5518,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626032</v>
+        <v>626130</v>
       </c>
       <c r="R45" t="n">
-        <v>6963816</v>
+        <v>6963689</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5590,32 +5590,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132998793</v>
+        <v>132998833</v>
       </c>
       <c r="B46" t="n">
-        <v>91918</v>
+        <v>92378</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5625,13 +5625,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626130</v>
+        <v>626072</v>
       </c>
       <c r="R46" t="n">
-        <v>6963689</v>
+        <v>6963711</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5697,32 +5697,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132998833</v>
+        <v>132998824</v>
       </c>
       <c r="B47" t="n">
-        <v>92378</v>
+        <v>91932</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626072</v>
+        <v>626032</v>
       </c>
       <c r="R47" t="n">
-        <v>6963711</v>
+        <v>6963816</v>
       </c>
       <c r="S47" t="n">
         <v>6</v>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6044,10 +6044,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132998818</v>
+        <v>132998794</v>
       </c>
       <c r="B50" t="n">
-        <v>92217</v>
+        <v>57955</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6055,34 +6055,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626014</v>
+        <v>626127</v>
       </c>
       <c r="R50" t="n">
-        <v>6963833</v>
+        <v>6963690</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6114,7 +6122,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6124,7 +6132,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6151,7 +6159,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132998796</v>
+        <v>132998818</v>
       </c>
       <c r="B51" t="n">
         <v>92217</v>
@@ -6186,10 +6194,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626152</v>
+        <v>626014</v>
       </c>
       <c r="R51" t="n">
-        <v>6963711</v>
+        <v>6963833</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6221,7 +6229,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6231,7 +6239,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6258,10 +6266,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132998794</v>
+        <v>132998796</v>
       </c>
       <c r="B52" t="n">
-        <v>57955</v>
+        <v>92217</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6269,42 +6277,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626127</v>
+        <v>626152</v>
       </c>
       <c r="R52" t="n">
-        <v>6963690</v>
+        <v>6963711</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6480,10 +6480,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132998848</v>
+        <v>132998807</v>
       </c>
       <c r="B54" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6491,34 +6491,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>625948</v>
+        <v>625962</v>
       </c>
       <c r="R54" t="n">
-        <v>6963689</v>
+        <v>6963840</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6550,7 +6558,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6560,7 +6568,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6587,10 +6600,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132998841</v>
+        <v>132998843</v>
       </c>
       <c r="B55" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6598,34 +6611,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626052</v>
+        <v>626021</v>
       </c>
       <c r="R55" t="n">
-        <v>6963684</v>
+        <v>6963665</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6657,7 +6678,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6667,7 +6688,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6694,10 +6720,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132998807</v>
+        <v>132998848</v>
       </c>
       <c r="B56" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6705,42 +6731,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>625962</v>
+        <v>625948</v>
       </c>
       <c r="R56" t="n">
-        <v>6963840</v>
+        <v>6963689</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6772,7 +6790,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6782,12 +6800,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6814,10 +6827,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132998843</v>
+        <v>132998841</v>
       </c>
       <c r="B57" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6825,42 +6838,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626021</v>
+        <v>626052</v>
       </c>
       <c r="R57" t="n">
-        <v>6963665</v>
+        <v>6963684</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6892,7 +6897,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6902,12 +6907,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6934,10 +6934,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132998834</v>
+        <v>132998813</v>
       </c>
       <c r="B58" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6945,21 +6945,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626079</v>
+        <v>626015</v>
       </c>
       <c r="R58" t="n">
-        <v>6963709</v>
+        <v>6963874</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7041,10 +7041,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132998813</v>
+        <v>132998834</v>
       </c>
       <c r="B59" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7052,21 +7052,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7076,10 +7076,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>626015</v>
+        <v>626079</v>
       </c>
       <c r="R59" t="n">
-        <v>6963874</v>
+        <v>6963709</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7589,10 +7589,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132998842</v>
+        <v>132998846</v>
       </c>
       <c r="B64" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7600,21 +7600,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>626052</v>
+        <v>625949</v>
       </c>
       <c r="R64" t="n">
-        <v>6963682</v>
+        <v>6963692</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7696,10 +7696,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132998846</v>
+        <v>132998842</v>
       </c>
       <c r="B65" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7707,21 +7707,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>625949</v>
+        <v>626052</v>
       </c>
       <c r="R65" t="n">
-        <v>6963692</v>
+        <v>6963682</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7803,53 +7803,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132998870</v>
+        <v>132998855</v>
       </c>
       <c r="B66" t="n">
-        <v>57958</v>
+        <v>101338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>626031</v>
+        <v>625891</v>
       </c>
       <c r="R66" t="n">
-        <v>6963761</v>
+        <v>6963678</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7881,7 +7873,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7891,12 +7883,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7923,45 +7910,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132998855</v>
+        <v>132998870</v>
       </c>
       <c r="B67" t="n">
-        <v>101338</v>
+        <v>57958</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>625891</v>
+        <v>626031</v>
       </c>
       <c r="R67" t="n">
-        <v>6963678</v>
+        <v>6963761</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7993,7 +7988,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8003,7 +7998,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8821,27 +8821,27 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132998831</v>
+        <v>132998835</v>
       </c>
       <c r="B75" t="n">
-        <v>57958</v>
+        <v>5199</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8850,11 +8850,12 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -8864,10 +8865,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>626039</v>
+        <v>626076</v>
       </c>
       <c r="R75" t="n">
-        <v>6963715</v>
+        <v>6963703</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8899,7 +8900,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8909,12 +8910,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8923,6 +8919,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8941,10 +8938,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132998810</v>
+        <v>132998823</v>
       </c>
       <c r="B76" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8952,45 +8949,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>625992</v>
+        <v>626030</v>
       </c>
       <c r="R76" t="n">
-        <v>6963864</v>
+        <v>6963820</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9019,7 +9008,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9029,12 +9018,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9061,54 +9045,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132998835</v>
+        <v>132998862</v>
       </c>
       <c r="B77" t="n">
-        <v>5199</v>
+        <v>92614</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>105930</v>
+        <v>898</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>626076</v>
+        <v>625946</v>
       </c>
       <c r="R77" t="n">
-        <v>6963703</v>
+        <v>6963712</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9140,7 +9115,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9150,7 +9125,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9159,7 +9134,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9290,10 +9264,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132998823</v>
+        <v>132998799</v>
       </c>
       <c r="B79" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9301,21 +9275,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9325,13 +9299,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>626030</v>
+        <v>626135</v>
       </c>
       <c r="R79" t="n">
-        <v>6963820</v>
+        <v>6963715</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9360,7 +9334,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9370,7 +9344,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9397,10 +9371,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132998799</v>
+        <v>132998831</v>
       </c>
       <c r="B80" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9408,31 +9382,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>626135</v>
+        <v>626039</v>
       </c>
       <c r="R80" t="n">
         <v>6963715</v>
@@ -9467,7 +9449,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9477,7 +9459,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9504,45 +9491,53 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132998862</v>
+        <v>132998810</v>
       </c>
       <c r="B81" t="n">
-        <v>92614</v>
+        <v>57958</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>625946</v>
+        <v>625992</v>
       </c>
       <c r="R81" t="n">
-        <v>6963712</v>
+        <v>6963864</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9574,7 +9569,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9584,7 +9579,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -3836,54 +3836,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132998865</v>
+        <v>132998849</v>
       </c>
       <c r="B30" t="n">
-        <v>5179</v>
+        <v>92217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625994</v>
+        <v>625938</v>
       </c>
       <c r="R30" t="n">
-        <v>6963702</v>
+        <v>6963688</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3915,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3925,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,7 +3925,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3953,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132998849</v>
+        <v>132998851</v>
       </c>
       <c r="B31" t="n">
-        <v>92217</v>
+        <v>91868</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3964,21 +3954,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3988,7 +3978,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625938</v>
+        <v>625937</v>
       </c>
       <c r="R31" t="n">
         <v>6963688</v>
@@ -4023,7 +4013,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4023,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132998851</v>
+        <v>132998860</v>
       </c>
       <c r="B32" t="n">
-        <v>91868</v>
+        <v>91932</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,21 +4061,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4095,10 +4085,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625937</v>
+        <v>625929</v>
       </c>
       <c r="R32" t="n">
-        <v>6963688</v>
+        <v>6963696</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4130,7 +4120,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4140,7 +4130,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,45 +4157,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132998860</v>
+        <v>132998865</v>
       </c>
       <c r="B33" t="n">
-        <v>91932</v>
+        <v>5179</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625929</v>
+        <v>625994</v>
       </c>
       <c r="R33" t="n">
-        <v>6963696</v>
+        <v>6963702</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4237,7 +4236,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4247,7 +4246,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,6 +4255,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -7148,10 +7148,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132998798</v>
+        <v>132998840</v>
       </c>
       <c r="B60" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7159,34 +7159,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>626159</v>
+        <v>626055</v>
       </c>
       <c r="R60" t="n">
-        <v>6963709</v>
+        <v>6963694</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7218,7 +7226,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7228,7 +7236,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7362,10 +7375,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132998840</v>
+        <v>132998798</v>
       </c>
       <c r="B62" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7373,42 +7386,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>626055</v>
+        <v>626159</v>
       </c>
       <c r="R62" t="n">
-        <v>6963694</v>
+        <v>6963709</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7440,7 +7445,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7450,12 +7455,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack på tall</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -3155,7 +3155,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132998820</v>
+        <v>132998819</v>
       </c>
       <c r="B24" t="n">
         <v>57958</v>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626040</v>
+        <v>626038</v>
       </c>
       <c r="R24" t="n">
-        <v>6963847</v>
+        <v>6963844</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Årsfärska ringhack på tall. Genomskinlig blänkande kåda syns med kikaren .</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,7 +3275,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132998819</v>
+        <v>132998820</v>
       </c>
       <c r="B25" t="n">
         <v>57958</v>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626038</v>
+        <v>626040</v>
       </c>
       <c r="R25" t="n">
-        <v>6963844</v>
+        <v>6963847</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Årsfärska ringhack på tall. Genomskinlig blänkande kåda syns med kikaren .</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3609,45 +3609,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132998801</v>
+        <v>132998872</v>
       </c>
       <c r="B28" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626119</v>
+        <v>626008</v>
       </c>
       <c r="R28" t="n">
-        <v>6963720</v>
+        <v>6963810</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3679,7 +3687,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,7 +3697,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3716,53 +3729,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132998872</v>
+        <v>132998801</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626008</v>
+        <v>626119</v>
       </c>
       <c r="R29" t="n">
-        <v>6963810</v>
+        <v>6963720</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3794,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,12 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,45 +3836,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132998849</v>
+        <v>132998865</v>
       </c>
       <c r="B30" t="n">
-        <v>92217</v>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625938</v>
+        <v>625994</v>
       </c>
       <c r="R30" t="n">
-        <v>6963688</v>
+        <v>6963702</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3915,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3925,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3925,6 +3934,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3943,10 +3953,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132998851</v>
+        <v>132998849</v>
       </c>
       <c r="B31" t="n">
-        <v>91868</v>
+        <v>92217</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3954,21 +3964,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3978,7 +3988,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625937</v>
+        <v>625938</v>
       </c>
       <c r="R31" t="n">
         <v>6963688</v>
@@ -4013,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4023,7 +4033,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132998860</v>
+        <v>132998851</v>
       </c>
       <c r="B32" t="n">
-        <v>91932</v>
+        <v>91868</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,21 +4071,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4085,10 +4095,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625929</v>
+        <v>625937</v>
       </c>
       <c r="R32" t="n">
-        <v>6963696</v>
+        <v>6963688</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4120,7 +4130,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4140,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4157,54 +4167,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132998865</v>
+        <v>132998860</v>
       </c>
       <c r="B33" t="n">
-        <v>5179</v>
+        <v>91932</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625994</v>
+        <v>625929</v>
       </c>
       <c r="R33" t="n">
-        <v>6963702</v>
+        <v>6963696</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4236,7 +4237,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4246,7 +4247,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4255,7 +4256,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132998874</v>
+        <v>132998836</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>92338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,21 +4606,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4630,13 +4630,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626066</v>
+        <v>626064</v>
       </c>
       <c r="R37" t="n">
-        <v>6963900</v>
+        <v>6963694</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4684,6 +4684,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4702,10 +4703,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132998811</v>
+        <v>132998874</v>
       </c>
       <c r="B38" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4713,42 +4714,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>625999</v>
+        <v>626066</v>
       </c>
       <c r="R38" t="n">
-        <v>6963864</v>
+        <v>6963900</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4780,7 +4773,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4790,12 +4783,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Årsfärskt ringhack på tall</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4822,7 +4810,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132998871</v>
+        <v>132998811</v>
       </c>
       <c r="B39" t="n">
         <v>57958</v>
@@ -4865,10 +4853,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626014</v>
+        <v>625999</v>
       </c>
       <c r="R39" t="n">
-        <v>6963802</v>
+        <v>6963864</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4900,7 +4888,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4910,12 +4898,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Årsfärskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,10 +4930,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132998836</v>
+        <v>132998871</v>
       </c>
       <c r="B40" t="n">
-        <v>92338</v>
+        <v>57958</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4953,37 +4941,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626064</v>
+        <v>626014</v>
       </c>
       <c r="R40" t="n">
-        <v>6963694</v>
+        <v>6963802</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5012,7 +5008,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5022,7 +5018,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5031,7 +5032,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132998794</v>
+        <v>132998818</v>
       </c>
       <c r="B50" t="n">
-        <v>57955</v>
+        <v>92217</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6055,42 +6055,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626127</v>
+        <v>626014</v>
       </c>
       <c r="R50" t="n">
-        <v>6963690</v>
+        <v>6963833</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6122,7 +6114,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6132,7 +6124,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6159,7 +6151,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132998818</v>
+        <v>132998796</v>
       </c>
       <c r="B51" t="n">
         <v>92217</v>
@@ -6194,10 +6186,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626014</v>
+        <v>626152</v>
       </c>
       <c r="R51" t="n">
-        <v>6963833</v>
+        <v>6963711</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6229,7 +6221,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6239,7 +6231,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6266,10 +6258,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132998796</v>
+        <v>132998794</v>
       </c>
       <c r="B52" t="n">
-        <v>92217</v>
+        <v>57955</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6277,34 +6269,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626152</v>
+        <v>626127</v>
       </c>
       <c r="R52" t="n">
-        <v>6963711</v>
+        <v>6963690</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6600,10 +6600,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132998843</v>
+        <v>132998848</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6611,42 +6611,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626021</v>
+        <v>625948</v>
       </c>
       <c r="R55" t="n">
-        <v>6963665</v>
+        <v>6963689</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6678,7 +6670,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6688,12 +6680,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6720,10 +6707,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132998848</v>
+        <v>132998843</v>
       </c>
       <c r="B56" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6731,34 +6718,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>625948</v>
+        <v>626021</v>
       </c>
       <c r="R56" t="n">
-        <v>6963689</v>
+        <v>6963665</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6790,7 +6785,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6800,7 +6795,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8821,57 +8821,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132998835</v>
+        <v>132998823</v>
       </c>
       <c r="B75" t="n">
-        <v>5199</v>
+        <v>92217</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>105930</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>626076</v>
+        <v>626030</v>
       </c>
       <c r="R75" t="n">
-        <v>6963703</v>
+        <v>6963820</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8900,7 +8891,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8910,7 +8901,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8919,7 +8910,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8938,32 +8928,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132998823</v>
+        <v>132998862</v>
       </c>
       <c r="B76" t="n">
-        <v>92217</v>
+        <v>92614</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8973,13 +8963,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>626030</v>
+        <v>625946</v>
       </c>
       <c r="R76" t="n">
-        <v>6963820</v>
+        <v>6963712</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9008,7 +8998,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9018,7 +9008,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9045,32 +9035,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132998862</v>
+        <v>132998828</v>
       </c>
       <c r="B77" t="n">
-        <v>92614</v>
+        <v>91918</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9080,10 +9070,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>625946</v>
+        <v>626045</v>
       </c>
       <c r="R77" t="n">
-        <v>6963712</v>
+        <v>6963763</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9115,7 +9105,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9125,7 +9115,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9152,7 +9147,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132998828</v>
+        <v>132998799</v>
       </c>
       <c r="B78" t="n">
         <v>91918</v>
@@ -9187,10 +9182,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>626045</v>
+        <v>626135</v>
       </c>
       <c r="R78" t="n">
-        <v>6963763</v>
+        <v>6963715</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9222,7 +9217,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9232,12 +9227,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9264,45 +9254,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132998799</v>
+        <v>132998835</v>
       </c>
       <c r="B79" t="n">
-        <v>91918</v>
+        <v>5199</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>626135</v>
+        <v>626076</v>
       </c>
       <c r="R79" t="n">
-        <v>6963715</v>
+        <v>6963703</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9334,7 +9333,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9344,7 +9343,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9353,6 +9352,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -3155,7 +3155,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132998819</v>
+        <v>132998820</v>
       </c>
       <c r="B24" t="n">
         <v>57958</v>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626038</v>
+        <v>626040</v>
       </c>
       <c r="R24" t="n">
-        <v>6963844</v>
+        <v>6963847</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Årsfärska ringhack på tall. Genomskinlig blänkande kåda syns med kikaren .</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,7 +3275,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132998820</v>
+        <v>132998819</v>
       </c>
       <c r="B25" t="n">
         <v>57958</v>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626040</v>
+        <v>626038</v>
       </c>
       <c r="R25" t="n">
-        <v>6963847</v>
+        <v>6963844</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Årsfärska ringhack på tall. Genomskinlig blänkande kåda syns med kikaren .</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3836,54 +3836,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132998865</v>
+        <v>132998849</v>
       </c>
       <c r="B30" t="n">
-        <v>5179</v>
+        <v>92217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625994</v>
+        <v>625938</v>
       </c>
       <c r="R30" t="n">
-        <v>6963702</v>
+        <v>6963688</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3915,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3925,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,7 +3925,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3953,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132998849</v>
+        <v>132998851</v>
       </c>
       <c r="B31" t="n">
-        <v>92217</v>
+        <v>91868</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3964,21 +3954,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3988,7 +3978,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625938</v>
+        <v>625937</v>
       </c>
       <c r="R31" t="n">
         <v>6963688</v>
@@ -4023,7 +4013,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4023,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132998851</v>
+        <v>132998860</v>
       </c>
       <c r="B32" t="n">
-        <v>91868</v>
+        <v>91932</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,21 +4061,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4095,10 +4085,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625937</v>
+        <v>625929</v>
       </c>
       <c r="R32" t="n">
-        <v>6963688</v>
+        <v>6963696</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4130,7 +4120,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4140,7 +4130,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,45 +4157,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132998860</v>
+        <v>132998865</v>
       </c>
       <c r="B33" t="n">
-        <v>91932</v>
+        <v>5179</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625929</v>
+        <v>625994</v>
       </c>
       <c r="R33" t="n">
-        <v>6963696</v>
+        <v>6963702</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4237,7 +4236,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4247,7 +4246,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,6 +4255,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132998818</v>
+        <v>132998794</v>
       </c>
       <c r="B50" t="n">
-        <v>92217</v>
+        <v>57955</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6055,34 +6055,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626014</v>
+        <v>626127</v>
       </c>
       <c r="R50" t="n">
-        <v>6963833</v>
+        <v>6963690</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6114,7 +6122,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6124,7 +6132,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6151,7 +6159,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132998796</v>
+        <v>132998818</v>
       </c>
       <c r="B51" t="n">
         <v>92217</v>
@@ -6186,10 +6194,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626152</v>
+        <v>626014</v>
       </c>
       <c r="R51" t="n">
-        <v>6963711</v>
+        <v>6963833</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6221,7 +6229,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6231,7 +6239,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6258,10 +6266,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132998794</v>
+        <v>132998796</v>
       </c>
       <c r="B52" t="n">
-        <v>57955</v>
+        <v>92217</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6269,42 +6277,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626127</v>
+        <v>626152</v>
       </c>
       <c r="R52" t="n">
-        <v>6963690</v>
+        <v>6963711</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6600,10 +6600,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132998848</v>
+        <v>132998843</v>
       </c>
       <c r="B55" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6611,34 +6611,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>625948</v>
+        <v>626021</v>
       </c>
       <c r="R55" t="n">
-        <v>6963689</v>
+        <v>6963665</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6670,7 +6678,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6680,7 +6688,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6707,10 +6720,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132998843</v>
+        <v>132998848</v>
       </c>
       <c r="B56" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6718,42 +6731,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626021</v>
+        <v>625948</v>
       </c>
       <c r="R56" t="n">
-        <v>6963665</v>
+        <v>6963689</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6785,7 +6790,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6795,12 +6800,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7482,32 +7482,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132998805</v>
+        <v>132998855</v>
       </c>
       <c r="B63" t="n">
-        <v>91932</v>
+        <v>101338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>626071</v>
+        <v>625891</v>
       </c>
       <c r="R63" t="n">
-        <v>6963769</v>
+        <v>6963678</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7589,10 +7589,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132998846</v>
+        <v>132998805</v>
       </c>
       <c r="B64" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7600,21 +7600,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>625949</v>
+        <v>626071</v>
       </c>
       <c r="R64" t="n">
-        <v>6963692</v>
+        <v>6963769</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7696,10 +7696,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132998842</v>
+        <v>132998846</v>
       </c>
       <c r="B65" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7707,21 +7707,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>626052</v>
+        <v>625949</v>
       </c>
       <c r="R65" t="n">
-        <v>6963682</v>
+        <v>6963692</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7803,32 +7803,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132998855</v>
+        <v>132998842</v>
       </c>
       <c r="B66" t="n">
-        <v>101338</v>
+        <v>92217</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>625891</v>
+        <v>626052</v>
       </c>
       <c r="R66" t="n">
-        <v>6963678</v>
+        <v>6963682</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -6600,10 +6600,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132998843</v>
+        <v>132998848</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6611,42 +6611,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626021</v>
+        <v>625948</v>
       </c>
       <c r="R55" t="n">
-        <v>6963665</v>
+        <v>6963689</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6678,7 +6670,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6688,12 +6680,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6720,10 +6707,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132998848</v>
+        <v>132998843</v>
       </c>
       <c r="B56" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6731,34 +6718,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>625948</v>
+        <v>626021</v>
       </c>
       <c r="R56" t="n">
-        <v>6963689</v>
+        <v>6963665</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6790,7 +6785,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6800,7 +6795,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1524,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132998868</v>
+        <v>132998804</v>
       </c>
       <c r="B9" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,21 +1535,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626006</v>
+        <v>626083</v>
       </c>
       <c r="R9" t="n">
-        <v>6963726</v>
+        <v>6963760</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,7 +1634,7 @@
         <v>132998853</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,32 +1738,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132998866</v>
+        <v>132998822</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>91883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>625993</v>
+        <v>626041</v>
       </c>
       <c r="R11" t="n">
-        <v>6963697</v>
+        <v>6963843</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,32 +1845,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132998859</v>
+        <v>132998821</v>
       </c>
       <c r="B12" t="n">
-        <v>92217</v>
+        <v>92380</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>625921</v>
+        <v>626044</v>
       </c>
       <c r="R12" t="n">
-        <v>6963711</v>
+        <v>6963850</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,12 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,32 +1952,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132998821</v>
+        <v>132998859</v>
       </c>
       <c r="B13" t="n">
-        <v>92378</v>
+        <v>92219</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626044</v>
+        <v>625921</v>
       </c>
       <c r="R13" t="n">
-        <v>6963850</v>
+        <v>6963711</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2027,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2032,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132998804</v>
+        <v>132998866</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626083</v>
+        <v>625993</v>
       </c>
       <c r="R14" t="n">
-        <v>6963760</v>
+        <v>6963697</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,32 +2171,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132998822</v>
+        <v>132998868</v>
       </c>
       <c r="B15" t="n">
-        <v>91881</v>
+        <v>91920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626041</v>
+        <v>626006</v>
       </c>
       <c r="R15" t="n">
-        <v>6963843</v>
+        <v>6963726</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2397,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132998837</v>
+        <v>132998825</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626063</v>
+        <v>626036</v>
       </c>
       <c r="R17" t="n">
-        <v>6963694</v>
+        <v>6963811</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,7 +2507,7 @@
         <v>132998863</v>
       </c>
       <c r="B18" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2611,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132998825</v>
+        <v>132998837</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2622,21 +2622,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626036</v>
+        <v>626063</v>
       </c>
       <c r="R19" t="n">
-        <v>6963811</v>
+        <v>6963694</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,7 +2721,7 @@
         <v>132998808</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,32 +2940,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132998852</v>
+        <v>132998856</v>
       </c>
       <c r="B22" t="n">
-        <v>92338</v>
+        <v>101340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040186</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625918</v>
+        <v>625873</v>
       </c>
       <c r="R22" t="n">
-        <v>6963673</v>
+        <v>6963710</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3029,7 +3029,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3048,32 +3047,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132998856</v>
+        <v>132998852</v>
       </c>
       <c r="B23" t="n">
-        <v>101338</v>
+        <v>92340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>6040186</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3083,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625873</v>
+        <v>625918</v>
       </c>
       <c r="R23" t="n">
-        <v>6963710</v>
+        <v>6963673</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3118,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3128,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,6 +3136,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132998869</v>
+        <v>132998876</v>
       </c>
       <c r="B26" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626014</v>
+        <v>626114</v>
       </c>
       <c r="R26" t="n">
-        <v>6963728</v>
+        <v>6963731</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3502,10 +3502,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132998876</v>
+        <v>132998869</v>
       </c>
       <c r="B27" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626114</v>
+        <v>626014</v>
       </c>
       <c r="R27" t="n">
-        <v>6963731</v>
+        <v>6963728</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,53 +3609,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132998872</v>
+        <v>132998801</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>91883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626008</v>
+        <v>626119</v>
       </c>
       <c r="R28" t="n">
-        <v>6963810</v>
+        <v>6963720</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3687,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3697,12 +3689,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,45 +3716,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132998801</v>
+        <v>132998872</v>
       </c>
       <c r="B29" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626119</v>
+        <v>626008</v>
       </c>
       <c r="R29" t="n">
-        <v>6963720</v>
+        <v>6963810</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3799,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3804,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,45 +3836,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132998849</v>
+        <v>132998865</v>
       </c>
       <c r="B30" t="n">
-        <v>92217</v>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625938</v>
+        <v>625994</v>
       </c>
       <c r="R30" t="n">
-        <v>6963688</v>
+        <v>6963702</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3915,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3925,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3925,6 +3934,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3943,10 +3953,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132998851</v>
+        <v>132998860</v>
       </c>
       <c r="B31" t="n">
-        <v>91868</v>
+        <v>91934</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3954,21 +3964,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3978,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625937</v>
+        <v>625929</v>
       </c>
       <c r="R31" t="n">
-        <v>6963688</v>
+        <v>6963696</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4013,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4023,7 +4033,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132998860</v>
+        <v>132998849</v>
       </c>
       <c r="B32" t="n">
-        <v>91932</v>
+        <v>92219</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,21 +4071,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4085,10 +4095,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625929</v>
+        <v>625938</v>
       </c>
       <c r="R32" t="n">
-        <v>6963696</v>
+        <v>6963688</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4120,7 +4130,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4140,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4157,54 +4167,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132998865</v>
+        <v>132998851</v>
       </c>
       <c r="B33" t="n">
-        <v>5179</v>
+        <v>91870</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>112</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625994</v>
+        <v>625937</v>
       </c>
       <c r="R33" t="n">
-        <v>6963702</v>
+        <v>6963688</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4236,7 +4237,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4246,7 +4247,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4255,7 +4256,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4274,10 +4274,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132998827</v>
+        <v>132998864</v>
       </c>
       <c r="B34" t="n">
-        <v>83181</v>
+        <v>91920</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,21 +4285,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4309,13 +4309,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626040</v>
+        <v>625948</v>
       </c>
       <c r="R34" t="n">
-        <v>6963809</v>
+        <v>6963705</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4381,10 +4381,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132998864</v>
+        <v>132998827</v>
       </c>
       <c r="B35" t="n">
-        <v>91918</v>
+        <v>83182</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,21 +4392,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625948</v>
+        <v>626040</v>
       </c>
       <c r="R35" t="n">
-        <v>6963705</v>
+        <v>6963809</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4491,7 +4491,7 @@
         <v>132998802</v>
       </c>
       <c r="B36" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132998836</v>
+        <v>132998874</v>
       </c>
       <c r="B37" t="n">
-        <v>92338</v>
+        <v>79334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,21 +4606,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4630,13 +4630,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626064</v>
+        <v>626066</v>
       </c>
       <c r="R37" t="n">
-        <v>6963694</v>
+        <v>6963900</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4684,7 +4684,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4703,10 +4702,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132998874</v>
+        <v>132998811</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4714,34 +4713,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626066</v>
+        <v>625999</v>
       </c>
       <c r="R38" t="n">
-        <v>6963900</v>
+        <v>6963864</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4773,7 +4780,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4783,7 +4790,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Årsfärskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4810,7 +4822,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132998811</v>
+        <v>132998871</v>
       </c>
       <c r="B39" t="n">
         <v>57958</v>
@@ -4853,10 +4865,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>625999</v>
+        <v>626014</v>
       </c>
       <c r="R39" t="n">
-        <v>6963864</v>
+        <v>6963802</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4888,7 +4900,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4898,12 +4910,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Årsfärskt ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4930,10 +4942,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132998871</v>
+        <v>132998836</v>
       </c>
       <c r="B40" t="n">
-        <v>57958</v>
+        <v>92340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4941,45 +4953,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626014</v>
+        <v>626064</v>
       </c>
       <c r="R40" t="n">
-        <v>6963802</v>
+        <v>6963694</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5008,7 +5012,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5018,12 +5022,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5032,6 +5031,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>132998814</v>
       </c>
       <c r="B41" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>132998797</v>
       </c>
       <c r="B42" t="n">
-        <v>92378</v>
+        <v>92380</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>132998830</v>
       </c>
       <c r="B43" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5376,45 +5376,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132998875</v>
+        <v>132998839</v>
       </c>
       <c r="B44" t="n">
-        <v>92378</v>
+        <v>57958</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626114</v>
+        <v>626063</v>
       </c>
       <c r="R44" t="n">
-        <v>6963731</v>
+        <v>6963696</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5446,7 +5454,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5456,7 +5464,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5483,10 +5496,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132998793</v>
+        <v>132998858</v>
       </c>
       <c r="B45" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5494,34 +5507,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626130</v>
+        <v>625898</v>
       </c>
       <c r="R45" t="n">
-        <v>6963689</v>
+        <v>6963724</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5553,7 +5574,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5563,7 +5584,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5590,10 +5616,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132998833</v>
+        <v>132998875</v>
       </c>
       <c r="B46" t="n">
-        <v>92378</v>
+        <v>92380</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5625,13 +5651,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626072</v>
+        <v>626114</v>
       </c>
       <c r="R46" t="n">
-        <v>6963711</v>
+        <v>6963731</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5660,7 +5686,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5670,7 +5696,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5700,7 +5726,7 @@
         <v>132998824</v>
       </c>
       <c r="B47" t="n">
-        <v>91932</v>
+        <v>91934</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5804,10 +5830,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132998839</v>
+        <v>132998793</v>
       </c>
       <c r="B48" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5815,42 +5841,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626063</v>
+        <v>626130</v>
       </c>
       <c r="R48" t="n">
-        <v>6963696</v>
+        <v>6963689</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5882,7 +5900,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5892,12 +5910,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5924,56 +5937,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132998858</v>
+        <v>132998833</v>
       </c>
       <c r="B49" t="n">
-        <v>57958</v>
+        <v>92380</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>625898</v>
+        <v>626072</v>
       </c>
       <c r="R49" t="n">
-        <v>6963724</v>
+        <v>6963711</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6002,7 +6007,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6012,12 +6017,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6044,10 +6044,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132998794</v>
+        <v>132998818</v>
       </c>
       <c r="B50" t="n">
-        <v>57955</v>
+        <v>92219</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6055,42 +6055,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626127</v>
+        <v>626014</v>
       </c>
       <c r="R50" t="n">
-        <v>6963690</v>
+        <v>6963833</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6122,7 +6114,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6132,7 +6124,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6159,10 +6151,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132998818</v>
+        <v>132998796</v>
       </c>
       <c r="B51" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6194,10 +6186,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626014</v>
+        <v>626152</v>
       </c>
       <c r="R51" t="n">
-        <v>6963833</v>
+        <v>6963711</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6229,7 +6221,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6239,7 +6231,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6266,10 +6258,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132998796</v>
+        <v>132998794</v>
       </c>
       <c r="B52" t="n">
-        <v>92217</v>
+        <v>57955</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6277,34 +6269,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626152</v>
+        <v>626127</v>
       </c>
       <c r="R52" t="n">
-        <v>6963711</v>
+        <v>6963690</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6376,7 +6376,7 @@
         <v>132998854</v>
       </c>
       <c r="B53" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132998807</v>
+        <v>132998848</v>
       </c>
       <c r="B54" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6491,42 +6491,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>625962</v>
+        <v>625948</v>
       </c>
       <c r="R54" t="n">
-        <v>6963840</v>
+        <v>6963689</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6558,7 +6550,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6568,12 +6560,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6600,10 +6587,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132998848</v>
+        <v>132998841</v>
       </c>
       <c r="B55" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6635,10 +6622,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>625948</v>
+        <v>626052</v>
       </c>
       <c r="R55" t="n">
-        <v>6963689</v>
+        <v>6963684</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6670,7 +6657,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6680,7 +6667,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6707,7 +6694,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132998843</v>
+        <v>132998807</v>
       </c>
       <c r="B56" t="n">
         <v>57958</v>
@@ -6750,10 +6737,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626021</v>
+        <v>625962</v>
       </c>
       <c r="R56" t="n">
-        <v>6963665</v>
+        <v>6963840</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6785,7 +6772,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6795,7 +6782,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -6827,10 +6814,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132998841</v>
+        <v>132998843</v>
       </c>
       <c r="B57" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6838,34 +6825,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626052</v>
+        <v>626021</v>
       </c>
       <c r="R57" t="n">
-        <v>6963684</v>
+        <v>6963665</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6897,7 +6892,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6907,7 +6902,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6934,10 +6934,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132998813</v>
+        <v>132998834</v>
       </c>
       <c r="B58" t="n">
-        <v>91918</v>
+        <v>91934</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6945,21 +6945,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626015</v>
+        <v>626079</v>
       </c>
       <c r="R58" t="n">
-        <v>6963874</v>
+        <v>6963709</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7041,10 +7041,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132998834</v>
+        <v>132998813</v>
       </c>
       <c r="B59" t="n">
-        <v>91932</v>
+        <v>91920</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7052,21 +7052,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7076,10 +7076,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>626079</v>
+        <v>626015</v>
       </c>
       <c r="R59" t="n">
-        <v>6963709</v>
+        <v>6963874</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7148,10 +7148,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132998840</v>
+        <v>132998798</v>
       </c>
       <c r="B60" t="n">
-        <v>57958</v>
+        <v>92219</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7159,42 +7159,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>626055</v>
+        <v>626159</v>
       </c>
       <c r="R60" t="n">
-        <v>6963694</v>
+        <v>6963709</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7226,7 +7218,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7236,12 +7228,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack på tall</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7271,7 +7258,7 @@
         <v>132998829</v>
       </c>
       <c r="B61" t="n">
-        <v>91932</v>
+        <v>91934</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7375,10 +7362,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132998798</v>
+        <v>132998840</v>
       </c>
       <c r="B62" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7386,34 +7373,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>626159</v>
+        <v>626055</v>
       </c>
       <c r="R62" t="n">
-        <v>6963709</v>
+        <v>6963694</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7445,7 +7440,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7455,7 +7450,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7482,32 +7482,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132998855</v>
+        <v>132998805</v>
       </c>
       <c r="B63" t="n">
-        <v>101338</v>
+        <v>91934</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>625891</v>
+        <v>626071</v>
       </c>
       <c r="R63" t="n">
-        <v>6963678</v>
+        <v>6963769</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7589,10 +7589,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132998805</v>
+        <v>132998842</v>
       </c>
       <c r="B64" t="n">
-        <v>91932</v>
+        <v>92219</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7600,21 +7600,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>626071</v>
+        <v>626052</v>
       </c>
       <c r="R64" t="n">
-        <v>6963769</v>
+        <v>6963682</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7699,7 +7699,7 @@
         <v>132998846</v>
       </c>
       <c r="B65" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132998842</v>
+        <v>132998870</v>
       </c>
       <c r="B66" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7814,34 +7814,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>626052</v>
+        <v>626031</v>
       </c>
       <c r="R66" t="n">
-        <v>6963682</v>
+        <v>6963761</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7873,7 +7881,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7883,7 +7891,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7910,53 +7923,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132998870</v>
+        <v>132998855</v>
       </c>
       <c r="B67" t="n">
-        <v>57958</v>
+        <v>101340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>626031</v>
+        <v>625891</v>
       </c>
       <c r="R67" t="n">
-        <v>6963761</v>
+        <v>6963678</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7988,7 +7993,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7998,12 +8003,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8030,45 +8030,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132998845</v>
+        <v>132998815</v>
       </c>
       <c r="B68" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>625958</v>
+        <v>626009</v>
       </c>
       <c r="R68" t="n">
-        <v>6963695</v>
+        <v>6963855</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8100,7 +8108,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8110,7 +8118,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8137,7 +8150,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132998815</v>
+        <v>132998806</v>
       </c>
       <c r="B69" t="n">
         <v>57958</v>
@@ -8165,12 +8178,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8180,10 +8201,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>626009</v>
+        <v>626016</v>
       </c>
       <c r="R69" t="n">
-        <v>6963855</v>
+        <v>6963766</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8215,7 +8236,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8225,12 +8246,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8257,61 +8273,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132998806</v>
+        <v>132998845</v>
       </c>
       <c r="B70" t="n">
-        <v>57958</v>
+        <v>91883</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>626016</v>
+        <v>625958</v>
       </c>
       <c r="R70" t="n">
-        <v>6963766</v>
+        <v>6963695</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8383,7 +8383,7 @@
         <v>132998832</v>
       </c>
       <c r="B71" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>132998817</v>
       </c>
       <c r="B72" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>132998795</v>
       </c>
       <c r="B73" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8821,10 +8821,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132998823</v>
+        <v>132998828</v>
       </c>
       <c r="B75" t="n">
-        <v>92217</v>
+        <v>91920</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8832,21 +8832,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8856,13 +8856,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>626030</v>
+        <v>626045</v>
       </c>
       <c r="R75" t="n">
-        <v>6963820</v>
+        <v>6963763</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8901,7 +8901,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8928,32 +8933,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132998862</v>
+        <v>132998823</v>
       </c>
       <c r="B76" t="n">
-        <v>92614</v>
+        <v>92219</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8963,13 +8968,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>625946</v>
+        <v>626030</v>
       </c>
       <c r="R76" t="n">
-        <v>6963712</v>
+        <v>6963820</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8998,7 +9003,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9008,7 +9013,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9035,10 +9040,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132998828</v>
+        <v>132998799</v>
       </c>
       <c r="B77" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9070,10 +9075,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>626045</v>
+        <v>626135</v>
       </c>
       <c r="R77" t="n">
-        <v>6963763</v>
+        <v>6963715</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9105,7 +9110,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9115,12 +9120,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9147,32 +9147,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132998799</v>
+        <v>132998862</v>
       </c>
       <c r="B78" t="n">
-        <v>91918</v>
+        <v>92616</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9182,10 +9182,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>626135</v>
+        <v>625946</v>
       </c>
       <c r="R78" t="n">
-        <v>6963715</v>
+        <v>6963712</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9614,7 +9614,7 @@
         <v>132999282</v>
       </c>
       <c r="B82" t="n">
-        <v>92566</v>
+        <v>92568</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -3836,54 +3836,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132998865</v>
+        <v>132998860</v>
       </c>
       <c r="B30" t="n">
-        <v>5179</v>
+        <v>91934</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625994</v>
+        <v>625929</v>
       </c>
       <c r="R30" t="n">
-        <v>6963702</v>
+        <v>6963696</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3915,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3925,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,7 +3925,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3953,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132998860</v>
+        <v>132998849</v>
       </c>
       <c r="B31" t="n">
-        <v>91934</v>
+        <v>92219</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3964,21 +3954,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3988,10 +3978,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625929</v>
+        <v>625938</v>
       </c>
       <c r="R31" t="n">
-        <v>6963696</v>
+        <v>6963688</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4023,7 +4013,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4023,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132998849</v>
+        <v>132998851</v>
       </c>
       <c r="B32" t="n">
-        <v>92219</v>
+        <v>91870</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,21 +4061,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4095,7 +4085,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625938</v>
+        <v>625937</v>
       </c>
       <c r="R32" t="n">
         <v>6963688</v>
@@ -4130,7 +4120,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4140,7 +4130,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,45 +4157,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132998851</v>
+        <v>132998865</v>
       </c>
       <c r="B33" t="n">
-        <v>91870</v>
+        <v>5179</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>112</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625937</v>
+        <v>625994</v>
       </c>
       <c r="R33" t="n">
-        <v>6963688</v>
+        <v>6963702</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4237,7 +4236,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4247,7 +4246,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,6 +4255,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -5376,53 +5376,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132998839</v>
+        <v>132998875</v>
       </c>
       <c r="B44" t="n">
-        <v>57958</v>
+        <v>92380</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626063</v>
+        <v>626114</v>
       </c>
       <c r="R44" t="n">
-        <v>6963696</v>
+        <v>6963731</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5454,7 +5446,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5464,12 +5456,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5496,10 +5483,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132998858</v>
+        <v>132998824</v>
       </c>
       <c r="B45" t="n">
-        <v>57958</v>
+        <v>91934</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5507,45 +5494,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>625898</v>
+        <v>626032</v>
       </c>
       <c r="R45" t="n">
-        <v>6963724</v>
+        <v>6963816</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5574,7 +5553,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5584,12 +5563,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5616,32 +5590,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132998875</v>
+        <v>132998793</v>
       </c>
       <c r="B46" t="n">
-        <v>92380</v>
+        <v>91920</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5651,10 +5625,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626114</v>
+        <v>626130</v>
       </c>
       <c r="R46" t="n">
-        <v>6963731</v>
+        <v>6963689</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5686,7 +5660,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5696,7 +5670,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5723,32 +5697,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132998824</v>
+        <v>132998833</v>
       </c>
       <c r="B47" t="n">
-        <v>91934</v>
+        <v>92380</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5758,10 +5732,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626032</v>
+        <v>626072</v>
       </c>
       <c r="R47" t="n">
-        <v>6963816</v>
+        <v>6963711</v>
       </c>
       <c r="S47" t="n">
         <v>6</v>
@@ -5793,7 +5767,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5803,7 +5777,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5830,10 +5804,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132998793</v>
+        <v>132998839</v>
       </c>
       <c r="B48" t="n">
-        <v>91920</v>
+        <v>57958</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5841,34 +5815,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626130</v>
+        <v>626063</v>
       </c>
       <c r="R48" t="n">
-        <v>6963689</v>
+        <v>6963696</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5900,7 +5882,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5910,7 +5892,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5937,48 +5924,56 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132998833</v>
+        <v>132998858</v>
       </c>
       <c r="B49" t="n">
-        <v>92380</v>
+        <v>57958</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>626072</v>
+        <v>625898</v>
       </c>
       <c r="R49" t="n">
-        <v>6963711</v>
+        <v>6963724</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6007,7 +6002,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6017,7 +6012,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -8821,45 +8821,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132998828</v>
+        <v>132998835</v>
       </c>
       <c r="B75" t="n">
-        <v>91920</v>
+        <v>5199</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>626045</v>
+        <v>626076</v>
       </c>
       <c r="R75" t="n">
-        <v>6963763</v>
+        <v>6963703</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8891,7 +8900,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8901,12 +8910,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8915,6 +8919,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8933,10 +8938,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132998823</v>
+        <v>132998828</v>
       </c>
       <c r="B76" t="n">
-        <v>92219</v>
+        <v>91920</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8944,21 +8949,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8968,13 +8973,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>626030</v>
+        <v>626045</v>
       </c>
       <c r="R76" t="n">
-        <v>6963820</v>
+        <v>6963763</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9003,7 +9008,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9013,7 +9018,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9040,10 +9050,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132998799</v>
+        <v>132998823</v>
       </c>
       <c r="B77" t="n">
-        <v>91920</v>
+        <v>92219</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9051,21 +9061,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9075,13 +9085,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>626135</v>
+        <v>626030</v>
       </c>
       <c r="R77" t="n">
-        <v>6963715</v>
+        <v>6963820</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9110,7 +9120,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9120,7 +9130,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9147,32 +9157,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132998862</v>
+        <v>132998799</v>
       </c>
       <c r="B78" t="n">
-        <v>92616</v>
+        <v>91920</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9182,10 +9192,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>625946</v>
+        <v>626135</v>
       </c>
       <c r="R78" t="n">
-        <v>6963712</v>
+        <v>6963715</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9217,7 +9227,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9227,7 +9237,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9254,54 +9264,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132998835</v>
+        <v>132998862</v>
       </c>
       <c r="B79" t="n">
-        <v>5199</v>
+        <v>92616</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>105930</v>
+        <v>898</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>626076</v>
+        <v>625946</v>
       </c>
       <c r="R79" t="n">
-        <v>6963703</v>
+        <v>6963712</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9333,7 +9334,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9343,7 +9344,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9352,7 +9353,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -7148,10 +7148,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132998798</v>
+        <v>132998840</v>
       </c>
       <c r="B60" t="n">
-        <v>92219</v>
+        <v>57958</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7159,34 +7159,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>626159</v>
+        <v>626055</v>
       </c>
       <c r="R60" t="n">
-        <v>6963709</v>
+        <v>6963694</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7218,7 +7226,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7228,7 +7236,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7255,10 +7268,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132998829</v>
+        <v>132998798</v>
       </c>
       <c r="B61" t="n">
-        <v>91934</v>
+        <v>92219</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7266,21 +7279,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7290,10 +7303,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>626048</v>
+        <v>626159</v>
       </c>
       <c r="R61" t="n">
-        <v>6963765</v>
+        <v>6963709</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7325,7 +7338,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7335,7 +7348,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7362,10 +7375,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132998840</v>
+        <v>132998829</v>
       </c>
       <c r="B62" t="n">
-        <v>57958</v>
+        <v>91934</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7373,42 +7386,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>626055</v>
+        <v>626048</v>
       </c>
       <c r="R62" t="n">
-        <v>6963694</v>
+        <v>6963765</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7440,7 +7445,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7450,12 +7455,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -1524,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132998804</v>
+        <v>132998853</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,21 +1535,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626083</v>
+        <v>625912</v>
       </c>
       <c r="R9" t="n">
-        <v>6963760</v>
+        <v>6963674</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,32 +1631,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132998853</v>
+        <v>132998821</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>92388</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625912</v>
+        <v>626044</v>
       </c>
       <c r="R10" t="n">
-        <v>6963674</v>
+        <v>6963850</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,32 +1738,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132998822</v>
+        <v>132998859</v>
       </c>
       <c r="B11" t="n">
-        <v>91883</v>
+        <v>92227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626041</v>
+        <v>625921</v>
       </c>
       <c r="R11" t="n">
-        <v>6963843</v>
+        <v>6963711</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1818,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,32 +1850,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132998821</v>
+        <v>132998866</v>
       </c>
       <c r="B12" t="n">
-        <v>92380</v>
+        <v>91928</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626044</v>
+        <v>625993</v>
       </c>
       <c r="R12" t="n">
-        <v>6963850</v>
+        <v>6963697</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1915,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132998859</v>
+        <v>132998868</v>
       </c>
       <c r="B13" t="n">
-        <v>92219</v>
+        <v>91928</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,21 +1968,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1987,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625921</v>
+        <v>626006</v>
       </c>
       <c r="R13" t="n">
-        <v>6963711</v>
+        <v>6963726</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2022,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,12 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132998866</v>
+        <v>132998844</v>
       </c>
       <c r="B14" t="n">
-        <v>91920</v>
+        <v>57136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,34 +2075,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625993</v>
+        <v>625974</v>
       </c>
       <c r="R14" t="n">
-        <v>6963697</v>
+        <v>6963670</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2134,7 +2146,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2156,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132998868</v>
+        <v>132998804</v>
       </c>
       <c r="B15" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,21 +2194,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2206,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626006</v>
+        <v>626083</v>
       </c>
       <c r="R15" t="n">
-        <v>6963726</v>
+        <v>6963760</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2241,7 +2253,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2263,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,60 +2290,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132998844</v>
+        <v>132998822</v>
       </c>
       <c r="B16" t="n">
-        <v>57136</v>
+        <v>91891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>625974</v>
+        <v>626041</v>
       </c>
       <c r="R16" t="n">
-        <v>6963670</v>
+        <v>6963843</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132998825</v>
+        <v>132998857</v>
       </c>
       <c r="B17" t="n">
-        <v>79334</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,37 +2408,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626036</v>
+        <v>625882</v>
       </c>
       <c r="R17" t="n">
-        <v>6963811</v>
+        <v>6963712</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2467,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132998863</v>
+        <v>132998852</v>
       </c>
       <c r="B18" t="n">
-        <v>92219</v>
+        <v>92348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,21 +2523,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6040186</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2539,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>625946</v>
+        <v>625918</v>
       </c>
       <c r="R18" t="n">
-        <v>6963712</v>
+        <v>6963673</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,7 +2582,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2592,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,6 +2601,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2611,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132998837</v>
+        <v>132998863</v>
       </c>
       <c r="B19" t="n">
-        <v>91920</v>
+        <v>92227</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2622,21 +2631,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2646,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626063</v>
+        <v>625946</v>
       </c>
       <c r="R19" t="n">
-        <v>6963694</v>
+        <v>6963712</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2681,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2700,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132998808</v>
+        <v>132998837</v>
       </c>
       <c r="B20" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,21 +2738,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2753,10 +2762,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625958</v>
+        <v>626063</v>
       </c>
       <c r="R20" t="n">
-        <v>6963846</v>
+        <v>6963694</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2788,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,10 +2834,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132998857</v>
+        <v>132998825</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,45 +2845,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625882</v>
+        <v>626036</v>
       </c>
       <c r="R21" t="n">
-        <v>6963712</v>
+        <v>6963811</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2903,7 +2904,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2914,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,32 +2941,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132998856</v>
+        <v>132998808</v>
       </c>
       <c r="B22" t="n">
-        <v>101340</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,10 +2976,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625873</v>
+        <v>625958</v>
       </c>
       <c r="R22" t="n">
-        <v>6963710</v>
+        <v>6963846</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3010,7 +3011,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3021,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,32 +3048,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132998852</v>
+        <v>132998856</v>
       </c>
       <c r="B23" t="n">
-        <v>92340</v>
+        <v>101348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3082,10 +3083,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625918</v>
+        <v>625873</v>
       </c>
       <c r="R23" t="n">
-        <v>6963673</v>
+        <v>6963710</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3117,7 +3118,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3128,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,7 +3137,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>132998876</v>
       </c>
       <c r="B26" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>132998869</v>
       </c>
       <c r="B27" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>132998801</v>
       </c>
       <c r="B28" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>132998860</v>
       </c>
       <c r="B30" t="n">
-        <v>91934</v>
+        <v>91942</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>132998849</v>
       </c>
       <c r="B31" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>132998851</v>
       </c>
       <c r="B32" t="n">
-        <v>91870</v>
+        <v>91878</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>132998864</v>
       </c>
       <c r="B34" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>132998827</v>
       </c>
       <c r="B35" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>132998802</v>
       </c>
       <c r="B36" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132998874</v>
+        <v>132998811</v>
       </c>
       <c r="B37" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,34 +4606,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626066</v>
+        <v>625999</v>
       </c>
       <c r="R37" t="n">
-        <v>6963900</v>
+        <v>6963864</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4665,7 +4673,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4675,7 +4683,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Årsfärskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4702,7 +4715,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132998811</v>
+        <v>132998871</v>
       </c>
       <c r="B38" t="n">
         <v>57958</v>
@@ -4745,10 +4758,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>625999</v>
+        <v>626014</v>
       </c>
       <c r="R38" t="n">
-        <v>6963864</v>
+        <v>6963802</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4780,7 +4793,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4790,12 +4803,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Årsfärskt ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4822,10 +4835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132998871</v>
+        <v>132998836</v>
       </c>
       <c r="B39" t="n">
-        <v>57958</v>
+        <v>92348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4833,45 +4846,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626014</v>
+        <v>626064</v>
       </c>
       <c r="R39" t="n">
-        <v>6963802</v>
+        <v>6963694</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4900,7 +4905,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4910,12 +4915,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4924,6 +4924,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4942,10 +4943,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132998836</v>
+        <v>132998874</v>
       </c>
       <c r="B40" t="n">
-        <v>92340</v>
+        <v>79334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4953,21 +4954,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4977,13 +4978,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626064</v>
+        <v>626066</v>
       </c>
       <c r="R40" t="n">
-        <v>6963694</v>
+        <v>6963900</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5012,7 +5013,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5022,7 +5023,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5031,7 +5032,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>132998814</v>
       </c>
       <c r="B41" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>132998797</v>
       </c>
       <c r="B42" t="n">
-        <v>92380</v>
+        <v>92388</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>132998830</v>
       </c>
       <c r="B43" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>132998875</v>
       </c>
       <c r="B44" t="n">
-        <v>92380</v>
+        <v>92388</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>132998824</v>
       </c>
       <c r="B45" t="n">
-        <v>91934</v>
+        <v>91942</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>132998793</v>
       </c>
       <c r="B46" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>132998833</v>
       </c>
       <c r="B47" t="n">
-        <v>92380</v>
+        <v>92388</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132998818</v>
+        <v>132998794</v>
       </c>
       <c r="B50" t="n">
-        <v>92219</v>
+        <v>57955</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6055,34 +6055,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626014</v>
+        <v>626127</v>
       </c>
       <c r="R50" t="n">
-        <v>6963833</v>
+        <v>6963690</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6114,7 +6122,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6124,7 +6132,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6151,10 +6159,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132998796</v>
+        <v>132998818</v>
       </c>
       <c r="B51" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6186,10 +6194,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626152</v>
+        <v>626014</v>
       </c>
       <c r="R51" t="n">
-        <v>6963711</v>
+        <v>6963833</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6221,7 +6229,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6231,7 +6239,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6258,10 +6266,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132998794</v>
+        <v>132998796</v>
       </c>
       <c r="B52" t="n">
-        <v>57955</v>
+        <v>92227</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6269,42 +6277,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626127</v>
+        <v>626152</v>
       </c>
       <c r="R52" t="n">
-        <v>6963690</v>
+        <v>6963711</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6376,7 +6376,7 @@
         <v>132998854</v>
       </c>
       <c r="B53" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>132998848</v>
       </c>
       <c r="B54" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>132998841</v>
       </c>
       <c r="B55" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>132998834</v>
       </c>
       <c r="B58" t="n">
-        <v>91934</v>
+        <v>91942</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>132998813</v>
       </c>
       <c r="B59" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7148,10 +7148,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132998840</v>
+        <v>132998798</v>
       </c>
       <c r="B60" t="n">
-        <v>57958</v>
+        <v>92227</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7159,42 +7159,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>626055</v>
+        <v>626159</v>
       </c>
       <c r="R60" t="n">
-        <v>6963694</v>
+        <v>6963709</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7226,7 +7218,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7236,12 +7228,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack på tall</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7268,10 +7255,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132998798</v>
+        <v>132998829</v>
       </c>
       <c r="B61" t="n">
-        <v>92219</v>
+        <v>91942</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7279,21 +7266,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7303,10 +7290,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>626159</v>
+        <v>626048</v>
       </c>
       <c r="R61" t="n">
-        <v>6963709</v>
+        <v>6963765</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7338,7 +7325,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7348,7 +7335,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7375,10 +7362,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132998829</v>
+        <v>132998840</v>
       </c>
       <c r="B62" t="n">
-        <v>91934</v>
+        <v>57958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7386,34 +7373,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>626048</v>
+        <v>626055</v>
       </c>
       <c r="R62" t="n">
-        <v>6963765</v>
+        <v>6963694</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7445,7 +7440,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7455,7 +7450,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7482,32 +7482,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132998805</v>
+        <v>132998855</v>
       </c>
       <c r="B63" t="n">
-        <v>91934</v>
+        <v>101348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>626071</v>
+        <v>625891</v>
       </c>
       <c r="R63" t="n">
-        <v>6963769</v>
+        <v>6963678</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7589,10 +7589,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132998842</v>
+        <v>132998805</v>
       </c>
       <c r="B64" t="n">
-        <v>92219</v>
+        <v>91942</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7600,21 +7600,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>626052</v>
+        <v>626071</v>
       </c>
       <c r="R64" t="n">
-        <v>6963682</v>
+        <v>6963769</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7696,10 +7696,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132998846</v>
+        <v>132998842</v>
       </c>
       <c r="B65" t="n">
-        <v>91920</v>
+        <v>92227</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7707,21 +7707,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>625949</v>
+        <v>626052</v>
       </c>
       <c r="R65" t="n">
-        <v>6963692</v>
+        <v>6963682</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7803,10 +7803,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132998870</v>
+        <v>132998846</v>
       </c>
       <c r="B66" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7814,42 +7814,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>626031</v>
+        <v>625949</v>
       </c>
       <c r="R66" t="n">
-        <v>6963761</v>
+        <v>6963692</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7881,7 +7873,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7891,12 +7883,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7923,45 +7910,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132998855</v>
+        <v>132998870</v>
       </c>
       <c r="B67" t="n">
-        <v>101340</v>
+        <v>57958</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>625891</v>
+        <v>626031</v>
       </c>
       <c r="R67" t="n">
-        <v>6963678</v>
+        <v>6963761</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7993,7 +7988,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8003,7 +7998,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8276,7 +8276,7 @@
         <v>132998845</v>
       </c>
       <c r="B70" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>132998832</v>
       </c>
       <c r="B71" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>132998817</v>
       </c>
       <c r="B72" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>132998795</v>
       </c>
       <c r="B73" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8821,27 +8821,27 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132998835</v>
+        <v>132998831</v>
       </c>
       <c r="B75" t="n">
-        <v>5199</v>
+        <v>57958</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8850,12 +8850,11 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -8865,10 +8864,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>626076</v>
+        <v>626039</v>
       </c>
       <c r="R75" t="n">
-        <v>6963703</v>
+        <v>6963715</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8900,7 +8899,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8910,7 +8909,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8919,7 +8923,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8938,10 +8941,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132998828</v>
+        <v>132998810</v>
       </c>
       <c r="B76" t="n">
-        <v>91920</v>
+        <v>57958</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8949,34 +8952,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>626045</v>
+        <v>625992</v>
       </c>
       <c r="R76" t="n">
-        <v>6963763</v>
+        <v>6963864</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9008,7 +9019,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9018,12 +9029,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Död fruktkropp</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9050,48 +9061,57 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132998823</v>
+        <v>132998835</v>
       </c>
       <c r="B77" t="n">
-        <v>92219</v>
+        <v>5199</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>105930</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>626030</v>
+        <v>626076</v>
       </c>
       <c r="R77" t="n">
-        <v>6963820</v>
+        <v>6963703</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9120,7 +9140,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9130,7 +9150,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9139,6 +9159,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9157,10 +9178,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132998799</v>
+        <v>132998828</v>
       </c>
       <c r="B78" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9192,10 +9213,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>626135</v>
+        <v>626045</v>
       </c>
       <c r="R78" t="n">
-        <v>6963715</v>
+        <v>6963763</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9227,7 +9248,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9237,7 +9258,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9264,32 +9290,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132998862</v>
+        <v>132998823</v>
       </c>
       <c r="B79" t="n">
-        <v>92616</v>
+        <v>92227</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9299,13 +9325,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>625946</v>
+        <v>626030</v>
       </c>
       <c r="R79" t="n">
-        <v>6963712</v>
+        <v>6963820</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9334,7 +9360,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9344,7 +9370,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9371,10 +9397,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132998831</v>
+        <v>132998799</v>
       </c>
       <c r="B80" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,39 +9408,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>626039</v>
+        <v>626135</v>
       </c>
       <c r="R80" t="n">
         <v>6963715</v>
@@ -9449,7 +9467,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9459,12 +9477,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9491,53 +9504,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132998810</v>
+        <v>132998862</v>
       </c>
       <c r="B81" t="n">
-        <v>57958</v>
+        <v>92624</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>625992</v>
+        <v>625946</v>
       </c>
       <c r="R81" t="n">
-        <v>6963864</v>
+        <v>6963712</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9569,7 +9574,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9579,12 +9584,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9614,7 +9614,7 @@
         <v>132999282</v>
       </c>
       <c r="B82" t="n">
-        <v>92568</v>
+        <v>92576</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -2064,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132998844</v>
+        <v>132998804</v>
       </c>
       <c r="B14" t="n">
-        <v>57136</v>
+        <v>79334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,46 +2075,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625974</v>
+        <v>626083</v>
       </c>
       <c r="R14" t="n">
-        <v>6963670</v>
+        <v>6963760</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2146,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2156,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,32 +2171,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132998804</v>
+        <v>132998822</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2218,13 +2206,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626083</v>
+        <v>626041</v>
       </c>
       <c r="R15" t="n">
-        <v>6963760</v>
+        <v>6963843</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2253,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2263,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,48 +2278,60 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132998822</v>
+        <v>132998844</v>
       </c>
       <c r="B16" t="n">
-        <v>91891</v>
+        <v>57136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626041</v>
+        <v>625974</v>
       </c>
       <c r="R16" t="n">
-        <v>6963843</v>
+        <v>6963670</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132998857</v>
+        <v>132998863</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>92227</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,39 +2408,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625882</v>
+        <v>625946</v>
       </c>
       <c r="R17" t="n">
         <v>6963712</v>
@@ -2475,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132998852</v>
+        <v>132998837</v>
       </c>
       <c r="B18" t="n">
-        <v>92348</v>
+        <v>91928</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2523,21 +2515,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2547,10 +2539,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>625918</v>
+        <v>626063</v>
       </c>
       <c r="R18" t="n">
-        <v>6963673</v>
+        <v>6963694</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2582,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2592,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,7 +2593,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2620,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132998863</v>
+        <v>132998825</v>
       </c>
       <c r="B19" t="n">
-        <v>92227</v>
+        <v>79334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,21 +2622,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,13 +2646,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625946</v>
+        <v>626036</v>
       </c>
       <c r="R19" t="n">
-        <v>6963712</v>
+        <v>6963811</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2690,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2727,10 +2718,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132998837</v>
+        <v>132998808</v>
       </c>
       <c r="B20" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,21 +2729,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2762,10 +2753,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626063</v>
+        <v>625958</v>
       </c>
       <c r="R20" t="n">
-        <v>6963694</v>
+        <v>6963846</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2797,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,10 +2825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132998825</v>
+        <v>132998857</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>57955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,37 +2836,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626036</v>
+        <v>625882</v>
       </c>
       <c r="R21" t="n">
-        <v>6963811</v>
+        <v>6963712</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2904,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2914,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2941,32 +2940,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132998808</v>
+        <v>132998856</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>101348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2976,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625958</v>
+        <v>625873</v>
       </c>
       <c r="R22" t="n">
-        <v>6963846</v>
+        <v>6963710</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3011,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3021,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,32 +3047,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132998856</v>
+        <v>132998852</v>
       </c>
       <c r="B23" t="n">
-        <v>101348</v>
+        <v>92348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>6040186</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3083,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625873</v>
+        <v>625918</v>
       </c>
       <c r="R23" t="n">
-        <v>6963710</v>
+        <v>6963673</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3118,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3128,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,6 +3136,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3836,45 +3836,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132998860</v>
+        <v>132998865</v>
       </c>
       <c r="B30" t="n">
-        <v>91942</v>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625929</v>
+        <v>625994</v>
       </c>
       <c r="R30" t="n">
-        <v>6963696</v>
+        <v>6963702</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3915,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3925,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3925,6 +3934,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3943,10 +3953,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132998849</v>
+        <v>132998860</v>
       </c>
       <c r="B31" t="n">
-        <v>92227</v>
+        <v>91942</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3954,21 +3964,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3978,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625938</v>
+        <v>625929</v>
       </c>
       <c r="R31" t="n">
-        <v>6963688</v>
+        <v>6963696</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4013,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4023,7 +4033,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132998851</v>
+        <v>132998849</v>
       </c>
       <c r="B32" t="n">
-        <v>91878</v>
+        <v>92227</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,21 +4071,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4085,7 +4095,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625937</v>
+        <v>625938</v>
       </c>
       <c r="R32" t="n">
         <v>6963688</v>
@@ -4120,7 +4130,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4140,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4157,54 +4167,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132998865</v>
+        <v>132998851</v>
       </c>
       <c r="B33" t="n">
-        <v>5179</v>
+        <v>91878</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>112</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625994</v>
+        <v>625937</v>
       </c>
       <c r="R33" t="n">
-        <v>6963702</v>
+        <v>6963688</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4236,7 +4237,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4246,7 +4247,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4255,7 +4256,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132998794</v>
+        <v>132998818</v>
       </c>
       <c r="B50" t="n">
-        <v>57955</v>
+        <v>92227</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6055,42 +6055,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626127</v>
+        <v>626014</v>
       </c>
       <c r="R50" t="n">
-        <v>6963690</v>
+        <v>6963833</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6122,7 +6114,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6132,7 +6124,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6159,7 +6151,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132998818</v>
+        <v>132998796</v>
       </c>
       <c r="B51" t="n">
         <v>92227</v>
@@ -6194,10 +6186,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626014</v>
+        <v>626152</v>
       </c>
       <c r="R51" t="n">
-        <v>6963833</v>
+        <v>6963711</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6229,7 +6221,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6239,7 +6231,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6266,10 +6258,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132998796</v>
+        <v>132998794</v>
       </c>
       <c r="B52" t="n">
-        <v>92227</v>
+        <v>57955</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6277,34 +6269,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626152</v>
+        <v>626127</v>
       </c>
       <c r="R52" t="n">
-        <v>6963711</v>
+        <v>6963690</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -8030,53 +8030,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132998815</v>
+        <v>132998845</v>
       </c>
       <c r="B68" t="n">
-        <v>57958</v>
+        <v>91891</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>626009</v>
+        <v>625958</v>
       </c>
       <c r="R68" t="n">
-        <v>6963855</v>
+        <v>6963695</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8108,7 +8100,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8118,12 +8110,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8150,7 +8137,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132998806</v>
+        <v>132998815</v>
       </c>
       <c r="B69" t="n">
         <v>57958</v>
@@ -8178,20 +8165,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8201,10 +8180,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>626016</v>
+        <v>626009</v>
       </c>
       <c r="R69" t="n">
-        <v>6963766</v>
+        <v>6963855</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8236,7 +8215,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8246,7 +8225,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8273,45 +8257,61 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132998845</v>
+        <v>132998806</v>
       </c>
       <c r="B70" t="n">
-        <v>91891</v>
+        <v>57958</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>625958</v>
+        <v>626016</v>
       </c>
       <c r="R70" t="n">
-        <v>6963695</v>
+        <v>6963766</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -4835,10 +4835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132998836</v>
+        <v>132998874</v>
       </c>
       <c r="B39" t="n">
-        <v>92348</v>
+        <v>79334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4846,21 +4846,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4870,13 +4870,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626064</v>
+        <v>626066</v>
       </c>
       <c r="R39" t="n">
-        <v>6963694</v>
+        <v>6963900</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4924,7 +4924,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4943,10 +4942,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132998874</v>
+        <v>132998836</v>
       </c>
       <c r="B40" t="n">
-        <v>79334</v>
+        <v>92348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4954,21 +4953,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4978,13 +4977,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626066</v>
+        <v>626064</v>
       </c>
       <c r="R40" t="n">
-        <v>6963900</v>
+        <v>6963694</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5013,7 +5012,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5023,7 +5022,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5032,6 +5031,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -7482,45 +7482,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132998855</v>
+        <v>132998870</v>
       </c>
       <c r="B63" t="n">
-        <v>101348</v>
+        <v>57958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>625891</v>
+        <v>626031</v>
       </c>
       <c r="R63" t="n">
-        <v>6963678</v>
+        <v>6963761</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7552,7 +7560,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7562,7 +7570,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7589,32 +7602,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132998805</v>
+        <v>132998855</v>
       </c>
       <c r="B64" t="n">
-        <v>91942</v>
+        <v>101348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7624,10 +7637,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>626071</v>
+        <v>625891</v>
       </c>
       <c r="R64" t="n">
-        <v>6963769</v>
+        <v>6963678</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7659,7 +7672,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7669,7 +7682,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7696,10 +7709,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132998842</v>
+        <v>132998805</v>
       </c>
       <c r="B65" t="n">
-        <v>92227</v>
+        <v>91942</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7707,21 +7720,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7731,10 +7744,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>626052</v>
+        <v>626071</v>
       </c>
       <c r="R65" t="n">
-        <v>6963682</v>
+        <v>6963769</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7766,7 +7779,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7776,7 +7789,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7803,10 +7816,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132998846</v>
+        <v>132998842</v>
       </c>
       <c r="B66" t="n">
-        <v>91928</v>
+        <v>92227</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7814,21 +7827,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7838,10 +7851,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>625949</v>
+        <v>626052</v>
       </c>
       <c r="R66" t="n">
-        <v>6963692</v>
+        <v>6963682</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7873,7 +7886,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7883,7 +7896,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7910,10 +7923,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132998870</v>
+        <v>132998846</v>
       </c>
       <c r="B67" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7921,42 +7934,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>626031</v>
+        <v>625949</v>
       </c>
       <c r="R67" t="n">
-        <v>6963761</v>
+        <v>6963692</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7988,7 +7993,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7998,12 +8003,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8380,10 +8380,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132998832</v>
+        <v>132998809</v>
       </c>
       <c r="B71" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8391,34 +8391,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>626035</v>
+        <v>625979</v>
       </c>
       <c r="R71" t="n">
-        <v>6963715</v>
+        <v>6963852</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8450,7 +8458,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8460,7 +8468,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8487,10 +8500,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132998817</v>
+        <v>132998832</v>
       </c>
       <c r="B72" t="n">
-        <v>92227</v>
+        <v>91928</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8498,21 +8511,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8522,13 +8535,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>626001</v>
+        <v>626035</v>
       </c>
       <c r="R72" t="n">
-        <v>6963850</v>
+        <v>6963715</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8557,7 +8570,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8567,7 +8580,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8594,10 +8607,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132998795</v>
+        <v>132998817</v>
       </c>
       <c r="B73" t="n">
-        <v>91928</v>
+        <v>92227</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8605,21 +8618,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8629,13 +8642,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>626128</v>
+        <v>626001</v>
       </c>
       <c r="R73" t="n">
-        <v>6963704</v>
+        <v>6963850</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8664,7 +8677,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8674,7 +8687,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8701,10 +8714,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132998809</v>
+        <v>132998795</v>
       </c>
       <c r="B74" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8712,42 +8725,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lamsatjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>625979</v>
+        <v>626128</v>
       </c>
       <c r="R74" t="n">
-        <v>6963852</v>
+        <v>6963704</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8779,7 +8784,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8789,12 +8794,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 4816-2024 artfynd.xlsx
+++ b/artfynd/A 4816-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998851</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132999282</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121127551</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998796</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998798</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998802</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998814</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998817</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998818</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998823</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998830</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1951,6 +2011,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998842</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2058,6 +2123,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998849</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998859</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998863</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998869</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998876</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998862</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2708,6 +2803,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17280637</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2815,6 +2915,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998793</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2922,6 +3027,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998795</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3029,6 +3139,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998799</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3136,6 +3251,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998813</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3248,6 +3368,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998828</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3355,6 +3480,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998832</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3462,6 +3592,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998837</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3569,6 +3704,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998841</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3676,6 +3816,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998846</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3783,6 +3928,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998848</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3890,6 +4040,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998853</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3997,6 +4152,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998864</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4104,6 +4264,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998866</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4211,6 +4376,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998868</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4318,6 +4488,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998805</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4425,6 +4600,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998824</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4532,6 +4712,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998829</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4639,6 +4824,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998834</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4746,6 +4936,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998860</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4853,6 +5048,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998797</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4960,6 +5160,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998821</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5067,6 +5272,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998833</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5174,6 +5384,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998875</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5281,6 +5496,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998827</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5388,6 +5608,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998801</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5495,6 +5720,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998822</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5602,6 +5832,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998845</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5712,6 +5947,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17278608</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5819,6 +6059,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998804</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5926,6 +6171,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998808</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6033,6 +6283,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998825</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6140,6 +6395,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998874</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6255,6 +6515,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998794</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6370,6 +6635,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998857</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6487,6 +6757,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121128629</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6610,6 +6885,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998806</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6730,6 +7010,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998807</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6850,6 +7135,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998809</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6970,6 +7260,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998810</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7090,6 +7385,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998811</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7210,6 +7510,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998815</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7330,6 +7635,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998819</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7450,6 +7760,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998820</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7570,6 +7885,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998831</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7690,6 +8010,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998839</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7810,6 +8135,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998840</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7930,6 +8260,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998843</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8050,6 +8385,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998858</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8170,6 +8510,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998870</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8290,6 +8635,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998871</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8410,6 +8760,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998872</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8527,6 +8882,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998865</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8646,6 +9006,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998844</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8763,6 +9128,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998835</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8870,6 +9240,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998854</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8977,6 +9352,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998855</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9084,6 +9464,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998856</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9192,6 +9577,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998836</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9300,8 +9690,93 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132998852</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>